--- a/99 - Excels/Open-LPs.xlsx
+++ b/99 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4CB781-BCBD-4C0C-90B7-FC1E1109C8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD30C6B4-5882-4FF5-8D08-B1E1343E7DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="368">
   <si>
     <t>LP</t>
   </si>
@@ -31,79 +31,1102 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-052098</t>
-  </si>
-  <si>
-    <t>LP-052015</t>
-  </si>
-  <si>
-    <t>LP-052310</t>
-  </si>
-  <si>
-    <t>LP-052625</t>
-  </si>
-  <si>
-    <t>LP-052723</t>
-  </si>
-  <si>
-    <t>LP-052788</t>
-  </si>
-  <si>
-    <t>LP-053081</t>
-  </si>
-  <si>
-    <t>LP-053082</t>
-  </si>
-  <si>
-    <t>LP-052550</t>
-  </si>
-  <si>
-    <t>LP-052747</t>
-  </si>
-  <si>
-    <t>LP-052751</t>
-  </si>
-  <si>
-    <t>LP-052774</t>
-  </si>
-  <si>
-    <t>LP-053054</t>
-  </si>
-  <si>
-    <t>LP-053053</t>
-  </si>
-  <si>
-    <t>LP-053080</t>
-  </si>
-  <si>
-    <t>LP-053083</t>
-  </si>
-  <si>
-    <t>LP-053084</t>
-  </si>
-  <si>
-    <t>LP-053085</t>
-  </si>
-  <si>
-    <t>LP-053086</t>
-  </si>
-  <si>
-    <t>LP-053092</t>
-  </si>
-  <si>
-    <t>LP-053096</t>
-  </si>
-  <si>
-    <t>LP-053097</t>
-  </si>
-  <si>
-    <t>LP-053098</t>
-  </si>
-  <si>
-    <t>LP-053419</t>
-  </si>
-  <si>
-    <t>Encerrado</t>
+    <t>LP-045241</t>
+  </si>
+  <si>
+    <t>LP-047639</t>
+  </si>
+  <si>
+    <t>LP-048170</t>
+  </si>
+  <si>
+    <t>LP-051018</t>
+  </si>
+  <si>
+    <t>LP-052552</t>
+  </si>
+  <si>
+    <t>LP-052814</t>
+  </si>
+  <si>
+    <t>LP-052815</t>
+  </si>
+  <si>
+    <t>LP-052816</t>
+  </si>
+  <si>
+    <t>LP-052817</t>
+  </si>
+  <si>
+    <t>LP-052874</t>
+  </si>
+  <si>
+    <t>LP-052931</t>
+  </si>
+  <si>
+    <t>LP-053213</t>
+  </si>
+  <si>
+    <t>LP-053267</t>
+  </si>
+  <si>
+    <t>LP-053270</t>
+  </si>
+  <si>
+    <t>LP-053485</t>
+  </si>
+  <si>
+    <t>LP-053497</t>
+  </si>
+  <si>
+    <t>LP-053528</t>
+  </si>
+  <si>
+    <t>LP-053571</t>
+  </si>
+  <si>
+    <t>LP-053575</t>
+  </si>
+  <si>
+    <t>LP-053789</t>
+  </si>
+  <si>
+    <t>LP-053861</t>
+  </si>
+  <si>
+    <t>LP-053970</t>
+  </si>
+  <si>
+    <t>LP-054102</t>
+  </si>
+  <si>
+    <t>LP-054103</t>
+  </si>
+  <si>
+    <t>LP-054104</t>
+  </si>
+  <si>
+    <t>LP-054109</t>
+  </si>
+  <si>
+    <t>LP-054666</t>
+  </si>
+  <si>
+    <t>LP-054675</t>
+  </si>
+  <si>
+    <t>LP-054729</t>
+  </si>
+  <si>
+    <t>LP-054775</t>
+  </si>
+  <si>
+    <t>LP-054777</t>
+  </si>
+  <si>
+    <t>LP-054837</t>
+  </si>
+  <si>
+    <t>LP-054843</t>
+  </si>
+  <si>
+    <t>LP-054855</t>
+  </si>
+  <si>
+    <t>LP-054859</t>
+  </si>
+  <si>
+    <t>LP-054882</t>
+  </si>
+  <si>
+    <t>LP-048005</t>
+  </si>
+  <si>
+    <t>LP-049933</t>
+  </si>
+  <si>
+    <t>LP-033118</t>
+  </si>
+  <si>
+    <t>LP-048737</t>
+  </si>
+  <si>
+    <t>LP-049335</t>
+  </si>
+  <si>
+    <t>LP-049354</t>
+  </si>
+  <si>
+    <t>LP-049830</t>
+  </si>
+  <si>
+    <t>LP-049956</t>
+  </si>
+  <si>
+    <t>LP-050092</t>
+  </si>
+  <si>
+    <t>LP-050237</t>
+  </si>
+  <si>
+    <t>LP-050243</t>
+  </si>
+  <si>
+    <t>LP-050252</t>
+  </si>
+  <si>
+    <t>LP-050308</t>
+  </si>
+  <si>
+    <t>LP-050661</t>
+  </si>
+  <si>
+    <t>LP-050662</t>
+  </si>
+  <si>
+    <t>LP-050687</t>
+  </si>
+  <si>
+    <t>LP-050742</t>
+  </si>
+  <si>
+    <t>LP-051000</t>
+  </si>
+  <si>
+    <t>LP-051225</t>
+  </si>
+  <si>
+    <t>LP-051308</t>
+  </si>
+  <si>
+    <t>LP-051392</t>
+  </si>
+  <si>
+    <t>LP-051450</t>
+  </si>
+  <si>
+    <t>LP-051527</t>
+  </si>
+  <si>
+    <t>LP-051546</t>
+  </si>
+  <si>
+    <t>LP-051715</t>
+  </si>
+  <si>
+    <t>LP-051778</t>
+  </si>
+  <si>
+    <t>LP-051808</t>
+  </si>
+  <si>
+    <t>LP-052208</t>
+  </si>
+  <si>
+    <t>LP-052223</t>
+  </si>
+  <si>
+    <t>LP-052286</t>
+  </si>
+  <si>
+    <t>LP-052287</t>
+  </si>
+  <si>
+    <t>LP-052315</t>
+  </si>
+  <si>
+    <t>LP-052325</t>
+  </si>
+  <si>
+    <t>LP-052388</t>
+  </si>
+  <si>
+    <t>LP-052407</t>
+  </si>
+  <si>
+    <t>LP-052676</t>
+  </si>
+  <si>
+    <t>LP-052679</t>
+  </si>
+  <si>
+    <t>LP-052725</t>
+  </si>
+  <si>
+    <t>LP-052731</t>
+  </si>
+  <si>
+    <t>LP-052750</t>
+  </si>
+  <si>
+    <t>LP-052793</t>
+  </si>
+  <si>
+    <t>LP-052871</t>
+  </si>
+  <si>
+    <t>LP-052899</t>
+  </si>
+  <si>
+    <t>LP-052900</t>
+  </si>
+  <si>
+    <t>LP-052916</t>
+  </si>
+  <si>
+    <t>LP-052991</t>
+  </si>
+  <si>
+    <t>LP-052992</t>
+  </si>
+  <si>
+    <t>LP-053020</t>
+  </si>
+  <si>
+    <t>LP-053021</t>
+  </si>
+  <si>
+    <t>LP-053022</t>
+  </si>
+  <si>
+    <t>LP-053027</t>
+  </si>
+  <si>
+    <t>LP-053029</t>
+  </si>
+  <si>
+    <t>LP-053056</t>
+  </si>
+  <si>
+    <t>LP-053057</t>
+  </si>
+  <si>
+    <t>LP-053060</t>
+  </si>
+  <si>
+    <t>LP-053063</t>
+  </si>
+  <si>
+    <t>LP-053090</t>
+  </si>
+  <si>
+    <t>LP-053091</t>
+  </si>
+  <si>
+    <t>LP-053093</t>
+  </si>
+  <si>
+    <t>LP-053228</t>
+  </si>
+  <si>
+    <t>LP-053230</t>
+  </si>
+  <si>
+    <t>LP-053238</t>
+  </si>
+  <si>
+    <t>LP-053249</t>
+  </si>
+  <si>
+    <t>LP-053255</t>
+  </si>
+  <si>
+    <t>LP-053257</t>
+  </si>
+  <si>
+    <t>LP-053266</t>
+  </si>
+  <si>
+    <t>LP-053305</t>
+  </si>
+  <si>
+    <t>LP-053446</t>
+  </si>
+  <si>
+    <t>LP-053563</t>
+  </si>
+  <si>
+    <t>LP-053565</t>
+  </si>
+  <si>
+    <t>LP-053717</t>
+  </si>
+  <si>
+    <t>LP-053796</t>
+  </si>
+  <si>
+    <t>LP-053898</t>
+  </si>
+  <si>
+    <t>LP-053904</t>
+  </si>
+  <si>
+    <t>LP-053930</t>
+  </si>
+  <si>
+    <t>LP-053942</t>
+  </si>
+  <si>
+    <t>LP-053949</t>
+  </si>
+  <si>
+    <t>LP-053951</t>
+  </si>
+  <si>
+    <t>LP-053953</t>
+  </si>
+  <si>
+    <t>LP-054181</t>
+  </si>
+  <si>
+    <t>LP-054183</t>
+  </si>
+  <si>
+    <t>LP-054188</t>
+  </si>
+  <si>
+    <t>LP-054349</t>
+  </si>
+  <si>
+    <t>LP-054393</t>
+  </si>
+  <si>
+    <t>LP-054549</t>
+  </si>
+  <si>
+    <t>LP-054550</t>
+  </si>
+  <si>
+    <t>LP-054551</t>
+  </si>
+  <si>
+    <t>LP-054553</t>
+  </si>
+  <si>
+    <t>LP-054581</t>
+  </si>
+  <si>
+    <t>LP-054623</t>
+  </si>
+  <si>
+    <t>LP-048367</t>
+  </si>
+  <si>
+    <t>LP-050448</t>
+  </si>
+  <si>
+    <t>LP-051075</t>
+  </si>
+  <si>
+    <t>LP-052398</t>
+  </si>
+  <si>
+    <t>LP-053210</t>
+  </si>
+  <si>
+    <t>LP-053239</t>
+  </si>
+  <si>
+    <t>LP-053253</t>
+  </si>
+  <si>
+    <t>LP-053903</t>
+  </si>
+  <si>
+    <t>LP-053915</t>
+  </si>
+  <si>
+    <t>LP-054186</t>
+  </si>
+  <si>
+    <t>LP-054211</t>
+  </si>
+  <si>
+    <t>LP-054552</t>
+  </si>
+  <si>
+    <t>LP-047971</t>
+  </si>
+  <si>
+    <t>LP-049433</t>
+  </si>
+  <si>
+    <t>LP-052888</t>
+  </si>
+  <si>
+    <t>LP-052389</t>
+  </si>
+  <si>
+    <t>LP-053192</t>
+  </si>
+  <si>
+    <t>LP-053530</t>
+  </si>
+  <si>
+    <t>LP-053531</t>
+  </si>
+  <si>
+    <t>LP-053532</t>
+  </si>
+  <si>
+    <t>LP-053566</t>
+  </si>
+  <si>
+    <t>LP-053630</t>
+  </si>
+  <si>
+    <t>LP-053660</t>
+  </si>
+  <si>
+    <t>LP-053729</t>
+  </si>
+  <si>
+    <t>LP-053809</t>
+  </si>
+  <si>
+    <t>LP-053829</t>
+  </si>
+  <si>
+    <t>LP-053848</t>
+  </si>
+  <si>
+    <t>LP-053850</t>
+  </si>
+  <si>
+    <t>LP-053918</t>
+  </si>
+  <si>
+    <t>LP-053923</t>
+  </si>
+  <si>
+    <t>LP-053924</t>
+  </si>
+  <si>
+    <t>LP-053966</t>
+  </si>
+  <si>
+    <t>LP-054061</t>
+  </si>
+  <si>
+    <t>LP-054073</t>
+  </si>
+  <si>
+    <t>LP-054077</t>
+  </si>
+  <si>
+    <t>LP-054078</t>
+  </si>
+  <si>
+    <t>LP-054080</t>
+  </si>
+  <si>
+    <t>LP-054089</t>
+  </si>
+  <si>
+    <t>LP-054099</t>
+  </si>
+  <si>
+    <t>LP-054120</t>
+  </si>
+  <si>
+    <t>LP-054121</t>
+  </si>
+  <si>
+    <t>LP-054124</t>
+  </si>
+  <si>
+    <t>LP-054127</t>
+  </si>
+  <si>
+    <t>LP-054145</t>
+  </si>
+  <si>
+    <t>LP-054147</t>
+  </si>
+  <si>
+    <t>LP-054148</t>
+  </si>
+  <si>
+    <t>LP-054149</t>
+  </si>
+  <si>
+    <t>LP-054150</t>
+  </si>
+  <si>
+    <t>LP-054155</t>
+  </si>
+  <si>
+    <t>LP-054157</t>
+  </si>
+  <si>
+    <t>LP-054193</t>
+  </si>
+  <si>
+    <t>LP-054199</t>
+  </si>
+  <si>
+    <t>LP-054200</t>
+  </si>
+  <si>
+    <t>LP-054232</t>
+  </si>
+  <si>
+    <t>LP-054235</t>
+  </si>
+  <si>
+    <t>LP-054238</t>
+  </si>
+  <si>
+    <t>LP-054239</t>
+  </si>
+  <si>
+    <t>LP-054387</t>
+  </si>
+  <si>
+    <t>LP-054427</t>
+  </si>
+  <si>
+    <t>LP-054449</t>
+  </si>
+  <si>
+    <t>LP-054465</t>
+  </si>
+  <si>
+    <t>LP-054674</t>
+  </si>
+  <si>
+    <t>LP-054678</t>
+  </si>
+  <si>
+    <t>LP-054747</t>
+  </si>
+  <si>
+    <t>LP-054807</t>
+  </si>
+  <si>
+    <t>LP-054816</t>
+  </si>
+  <si>
+    <t>LP-054853</t>
+  </si>
+  <si>
+    <t>LP-054866</t>
+  </si>
+  <si>
+    <t>LP-054940</t>
+  </si>
+  <si>
+    <t>LP-054951</t>
+  </si>
+  <si>
+    <t>LP-054992</t>
+  </si>
+  <si>
+    <t>LP-055019</t>
+  </si>
+  <si>
+    <t>LP-055022</t>
+  </si>
+  <si>
+    <t>LP-055025</t>
+  </si>
+  <si>
+    <t>LP-055054</t>
+  </si>
+  <si>
+    <t>LP-055056</t>
+  </si>
+  <si>
+    <t>LP-055062</t>
+  </si>
+  <si>
+    <t>LP-055109</t>
+  </si>
+  <si>
+    <t>LP-055112</t>
+  </si>
+  <si>
+    <t>LP-055139</t>
+  </si>
+  <si>
+    <t>LP-055184</t>
+  </si>
+  <si>
+    <t>LP-048723</t>
+  </si>
+  <si>
+    <t>LP-051848</t>
+  </si>
+  <si>
+    <t>LP-051849</t>
+  </si>
+  <si>
+    <t>LP-051850</t>
+  </si>
+  <si>
+    <t>LP-051851</t>
+  </si>
+  <si>
+    <t>LP-051853</t>
+  </si>
+  <si>
+    <t>LP-051863</t>
+  </si>
+  <si>
+    <t>LP-051864</t>
+  </si>
+  <si>
+    <t>LP-051867</t>
+  </si>
+  <si>
+    <t>LP-052833</t>
+  </si>
+  <si>
+    <t>LP-052884</t>
+  </si>
+  <si>
+    <t>LP-052885</t>
+  </si>
+  <si>
+    <t>LP-052964</t>
+  </si>
+  <si>
+    <t>LP-052969</t>
+  </si>
+  <si>
+    <t>LP-052981</t>
+  </si>
+  <si>
+    <t>LP-053016</t>
+  </si>
+  <si>
+    <t>LP-053195</t>
+  </si>
+  <si>
+    <t>LP-053329</t>
+  </si>
+  <si>
+    <t>LP-053387</t>
+  </si>
+  <si>
+    <t>LP-053529</t>
+  </si>
+  <si>
+    <t>LP-053533</t>
+  </si>
+  <si>
+    <t>LP-053628</t>
+  </si>
+  <si>
+    <t>LP-053735</t>
+  </si>
+  <si>
+    <t>LP-053736</t>
+  </si>
+  <si>
+    <t>LP-053737</t>
+  </si>
+  <si>
+    <t>LP-053738</t>
+  </si>
+  <si>
+    <t>LP-053739</t>
+  </si>
+  <si>
+    <t>LP-053740</t>
+  </si>
+  <si>
+    <t>LP-053741</t>
+  </si>
+  <si>
+    <t>LP-053742</t>
+  </si>
+  <si>
+    <t>LP-053743</t>
+  </si>
+  <si>
+    <t>LP-054066</t>
+  </si>
+  <si>
+    <t>LP-054119</t>
+  </si>
+  <si>
+    <t>LP-054068</t>
+  </si>
+  <si>
+    <t>LP-054069</t>
+  </si>
+  <si>
+    <t>LP-054105</t>
+  </si>
+  <si>
+    <t>LP-054106</t>
+  </si>
+  <si>
+    <t>LP-054107</t>
+  </si>
+  <si>
+    <t>LP-054108</t>
+  </si>
+  <si>
+    <t>LP-054118</t>
+  </si>
+  <si>
+    <t>LP-054122</t>
+  </si>
+  <si>
+    <t>LP-054221</t>
+  </si>
+  <si>
+    <t>LP-054222</t>
+  </si>
+  <si>
+    <t>LP-054224</t>
+  </si>
+  <si>
+    <t>LP-054505</t>
+  </si>
+  <si>
+    <t>LP-054659</t>
+  </si>
+  <si>
+    <t>LP-054667</t>
+  </si>
+  <si>
+    <t>LP-054673</t>
+  </si>
+  <si>
+    <t>LP-054686</t>
+  </si>
+  <si>
+    <t>LP-054811</t>
+  </si>
+  <si>
+    <t>LP-054852</t>
+  </si>
+  <si>
+    <t>LP-054718</t>
+  </si>
+  <si>
+    <t>LP-054723</t>
+  </si>
+  <si>
+    <t>LP-054724</t>
+  </si>
+  <si>
+    <t>LP-054725</t>
+  </si>
+  <si>
+    <t>LP-054726</t>
+  </si>
+  <si>
+    <t>LP-054727</t>
+  </si>
+  <si>
+    <t>LP-054728</t>
+  </si>
+  <si>
+    <t>LP-054786</t>
+  </si>
+  <si>
+    <t>LP-049613</t>
+  </si>
+  <si>
+    <t>LP-052648</t>
+  </si>
+  <si>
+    <t>LP-053283</t>
+  </si>
+  <si>
+    <t>LP-053534</t>
+  </si>
+  <si>
+    <t>LP-053846</t>
+  </si>
+  <si>
+    <t>LP-053847</t>
+  </si>
+  <si>
+    <t>LP-053902</t>
+  </si>
+  <si>
+    <t>LP-053919</t>
+  </si>
+  <si>
+    <t>LP-053921</t>
+  </si>
+  <si>
+    <t>LP-053973</t>
+  </si>
+  <si>
+    <t>LP-053975</t>
+  </si>
+  <si>
+    <t>LP-054081</t>
+  </si>
+  <si>
+    <t>LP-054092</t>
+  </si>
+  <si>
+    <t>LP-054093</t>
+  </si>
+  <si>
+    <t>LP-054094</t>
+  </si>
+  <si>
+    <t>LP-054095</t>
+  </si>
+  <si>
+    <t>LP-054096</t>
+  </si>
+  <si>
+    <t>LP-054097</t>
+  </si>
+  <si>
+    <t>LP-054236</t>
+  </si>
+  <si>
+    <t>LP-054453</t>
+  </si>
+  <si>
+    <t>LP-054454</t>
+  </si>
+  <si>
+    <t>LP-054467</t>
+  </si>
+  <si>
+    <t>LP-054637</t>
+  </si>
+  <si>
+    <t>LP-054680</t>
+  </si>
+  <si>
+    <t>LP-054863</t>
+  </si>
+  <si>
+    <t>LP-054851</t>
+  </si>
+  <si>
+    <t>LP-054864</t>
+  </si>
+  <si>
+    <t>LP-054865</t>
+  </si>
+  <si>
+    <t>LP-054934</t>
+  </si>
+  <si>
+    <t>LP-054937</t>
+  </si>
+  <si>
+    <t>LP-055036</t>
+  </si>
+  <si>
+    <t>LP-055041</t>
+  </si>
+  <si>
+    <t>LP-055213</t>
+  </si>
+  <si>
+    <t>LP-055215</t>
+  </si>
+  <si>
+    <t>LP-055218</t>
+  </si>
+  <si>
+    <t>LP-055222</t>
+  </si>
+  <si>
+    <t>LP-039318</t>
+  </si>
+  <si>
+    <t>LP-048361</t>
+  </si>
+  <si>
+    <t>LP-051397</t>
+  </si>
+  <si>
+    <t>LP-051532</t>
+  </si>
+  <si>
+    <t>LP-051689</t>
+  </si>
+  <si>
+    <t>LP-052355</t>
+  </si>
+  <si>
+    <t>LP-052898</t>
+  </si>
+  <si>
+    <t>LP-053058</t>
+  </si>
+  <si>
+    <t>LP-053250</t>
+  </si>
+  <si>
+    <t>LP-053291</t>
+  </si>
+  <si>
+    <t>LP-053840</t>
+  </si>
+  <si>
+    <t>LP-054013</t>
+  </si>
+  <si>
+    <t>LP-054091</t>
+  </si>
+  <si>
+    <t>LP-054216</t>
+  </si>
+  <si>
+    <t>LP-054273</t>
+  </si>
+  <si>
+    <t>LP-054274</t>
+  </si>
+  <si>
+    <t>LP-054275</t>
+  </si>
+  <si>
+    <t>LP-054276</t>
+  </si>
+  <si>
+    <t>LP-054396</t>
+  </si>
+  <si>
+    <t>LP-054471</t>
+  </si>
+  <si>
+    <t>LP-054862</t>
+  </si>
+  <si>
+    <t>LP-054939</t>
+  </si>
+  <si>
+    <t>LP-054947</t>
+  </si>
+  <si>
+    <t>LP-055005</t>
+  </si>
+  <si>
+    <t>LP-055141</t>
+  </si>
+  <si>
+    <t>LP-055183</t>
+  </si>
+  <si>
+    <t>LP-055298</t>
+  </si>
+  <si>
+    <t>LP-055316</t>
+  </si>
+  <si>
+    <t>LP-055409</t>
+  </si>
+  <si>
+    <t>LP-055412</t>
+  </si>
+  <si>
+    <t>LP-055413</t>
+  </si>
+  <si>
+    <t>LP-055425</t>
+  </si>
+  <si>
+    <t>LP-055426</t>
+  </si>
+  <si>
+    <t>LP-055448</t>
+  </si>
+  <si>
+    <t>LP-055453</t>
+  </si>
+  <si>
+    <t>LP-055458</t>
+  </si>
+  <si>
+    <t>LP-047118</t>
+  </si>
+  <si>
+    <t>LP-049644</t>
+  </si>
+  <si>
+    <t>LP-050253</t>
+  </si>
+  <si>
+    <t>LP-050762</t>
+  </si>
+  <si>
+    <t>LP-051345</t>
+  </si>
+  <si>
+    <t>LP-051352</t>
+  </si>
+  <si>
+    <t>LP-051443</t>
+  </si>
+  <si>
+    <t>LP-051786</t>
+  </si>
+  <si>
+    <t>LP-052186</t>
+  </si>
+  <si>
+    <t>LP-052373</t>
+  </si>
+  <si>
+    <t>LP-052408</t>
+  </si>
+  <si>
+    <t>LP-052709</t>
+  </si>
+  <si>
+    <t>LP-052906</t>
+  </si>
+  <si>
+    <t>LP-052914</t>
+  </si>
+  <si>
+    <t>LP-052977</t>
+  </si>
+  <si>
+    <t>LP-053062</t>
+  </si>
+  <si>
+    <t>LP-053089</t>
+  </si>
+  <si>
+    <t>LP-053471</t>
+  </si>
+  <si>
+    <t>LP-053507</t>
+  </si>
+  <si>
+    <t>LP-053728</t>
+  </si>
+  <si>
+    <t>LP-053895</t>
+  </si>
+  <si>
+    <t>LP-053896</t>
+  </si>
+  <si>
+    <t>LP-053913</t>
+  </si>
+  <si>
+    <t>LP-054010</t>
+  </si>
+  <si>
+    <t>LP-054166</t>
+  </si>
+  <si>
+    <t>LP-054210</t>
+  </si>
+  <si>
+    <t>LP-051348</t>
+  </si>
+  <si>
+    <t>LP-054620</t>
   </si>
 </sst>
 </file>
@@ -466,11 +1489,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -483,194 +1506,1842 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>26</v>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/Open-LPs.xlsx
+++ b/99 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD30C6B4-5882-4FF5-8D08-B1E1343E7DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CF322F-EA3D-4C77-9480-168525F66EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,27 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$230</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="231">
   <si>
     <t>LP</t>
   </si>
@@ -31,231 +44,30 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-045241</t>
-  </si>
-  <si>
-    <t>LP-047639</t>
-  </si>
-  <si>
-    <t>LP-048170</t>
-  </si>
-  <si>
-    <t>LP-051018</t>
-  </si>
-  <si>
-    <t>LP-052552</t>
-  </si>
-  <si>
-    <t>LP-052814</t>
-  </si>
-  <si>
-    <t>LP-052815</t>
-  </si>
-  <si>
-    <t>LP-052816</t>
-  </si>
-  <si>
-    <t>LP-052817</t>
-  </si>
-  <si>
-    <t>LP-052874</t>
-  </si>
-  <si>
-    <t>LP-052931</t>
-  </si>
-  <si>
-    <t>LP-053213</t>
-  </si>
-  <si>
-    <t>LP-053267</t>
-  </si>
-  <si>
-    <t>LP-053270</t>
-  </si>
-  <si>
-    <t>LP-053485</t>
-  </si>
-  <si>
-    <t>LP-053497</t>
-  </si>
-  <si>
-    <t>LP-053528</t>
-  </si>
-  <si>
     <t>LP-053571</t>
   </si>
   <si>
-    <t>LP-053575</t>
-  </si>
-  <si>
-    <t>LP-053789</t>
-  </si>
-  <si>
-    <t>LP-053861</t>
-  </si>
-  <si>
-    <t>LP-053970</t>
-  </si>
-  <si>
-    <t>LP-054102</t>
-  </si>
-  <si>
-    <t>LP-054103</t>
-  </si>
-  <si>
-    <t>LP-054104</t>
-  </si>
-  <si>
-    <t>LP-054109</t>
-  </si>
-  <si>
-    <t>LP-054666</t>
-  </si>
-  <si>
-    <t>LP-054675</t>
-  </si>
-  <si>
     <t>LP-054729</t>
   </si>
   <si>
-    <t>LP-054775</t>
-  </si>
-  <si>
-    <t>LP-054777</t>
-  </si>
-  <si>
-    <t>LP-054837</t>
-  </si>
-  <si>
-    <t>LP-054843</t>
-  </si>
-  <si>
-    <t>LP-054855</t>
-  </si>
-  <si>
-    <t>LP-054859</t>
-  </si>
-  <si>
-    <t>LP-054882</t>
-  </si>
-  <si>
-    <t>LP-048005</t>
-  </si>
-  <si>
-    <t>LP-049933</t>
-  </si>
-  <si>
-    <t>LP-033118</t>
-  </si>
-  <si>
-    <t>LP-048737</t>
-  </si>
-  <si>
     <t>LP-049335</t>
   </si>
   <si>
-    <t>LP-049354</t>
-  </si>
-  <si>
-    <t>LP-049830</t>
-  </si>
-  <si>
-    <t>LP-049956</t>
-  </si>
-  <si>
-    <t>LP-050092</t>
-  </si>
-  <si>
-    <t>LP-050237</t>
-  </si>
-  <si>
-    <t>LP-050243</t>
-  </si>
-  <si>
-    <t>LP-050252</t>
-  </si>
-  <si>
-    <t>LP-050308</t>
-  </si>
-  <si>
-    <t>LP-050661</t>
-  </si>
-  <si>
-    <t>LP-050662</t>
-  </si>
-  <si>
-    <t>LP-050687</t>
-  </si>
-  <si>
-    <t>LP-050742</t>
-  </si>
-  <si>
-    <t>LP-051000</t>
-  </si>
-  <si>
-    <t>LP-051225</t>
-  </si>
-  <si>
-    <t>LP-051308</t>
-  </si>
-  <si>
-    <t>LP-051392</t>
-  </si>
-  <si>
-    <t>LP-051450</t>
-  </si>
-  <si>
-    <t>LP-051527</t>
-  </si>
-  <si>
-    <t>LP-051546</t>
-  </si>
-  <si>
-    <t>LP-051715</t>
+    <t>Apropriar na CJ88</t>
   </si>
   <si>
     <t>LP-051778</t>
   </si>
   <si>
-    <t>LP-051808</t>
-  </si>
-  <si>
-    <t>LP-052208</t>
-  </si>
-  <si>
-    <t>LP-052223</t>
-  </si>
-  <si>
-    <t>LP-052286</t>
-  </si>
-  <si>
-    <t>LP-052287</t>
-  </si>
-  <si>
-    <t>LP-052315</t>
-  </si>
-  <si>
-    <t>LP-052325</t>
-  </si>
-  <si>
-    <t>LP-052388</t>
-  </si>
-  <si>
     <t>LP-052407</t>
   </si>
   <si>
     <t>LP-052676</t>
   </si>
   <si>
-    <t>LP-052679</t>
-  </si>
-  <si>
     <t>LP-052725</t>
   </si>
   <si>
-    <t>LP-052731</t>
-  </si>
-  <si>
     <t>LP-052750</t>
   </si>
   <si>
@@ -268,9 +80,6 @@
     <t>LP-052899</t>
   </si>
   <si>
-    <t>LP-052900</t>
-  </si>
-  <si>
     <t>LP-052916</t>
   </si>
   <si>
@@ -280,93 +89,30 @@
     <t>LP-052992</t>
   </si>
   <si>
-    <t>LP-053020</t>
-  </si>
-  <si>
-    <t>LP-053021</t>
-  </si>
-  <si>
-    <t>LP-053022</t>
-  </si>
-  <si>
-    <t>LP-053027</t>
-  </si>
-  <si>
     <t>LP-053029</t>
   </si>
   <si>
-    <t>LP-053056</t>
-  </si>
-  <si>
-    <t>LP-053057</t>
-  </si>
-  <si>
-    <t>LP-053060</t>
-  </si>
-  <si>
-    <t>LP-053063</t>
-  </si>
-  <si>
-    <t>LP-053090</t>
-  </si>
-  <si>
-    <t>LP-053091</t>
-  </si>
-  <si>
-    <t>LP-053093</t>
-  </si>
-  <si>
-    <t>LP-053228</t>
-  </si>
-  <si>
-    <t>LP-053230</t>
-  </si>
-  <si>
-    <t>LP-053238</t>
+    <t>LP-053210</t>
   </si>
   <si>
     <t>LP-053249</t>
   </si>
   <si>
+    <t>LP-053253</t>
+  </si>
+  <si>
     <t>LP-053255</t>
   </si>
   <si>
     <t>LP-053257</t>
   </si>
   <si>
-    <t>LP-053266</t>
-  </si>
-  <si>
-    <t>LP-053305</t>
-  </si>
-  <si>
-    <t>LP-053446</t>
-  </si>
-  <si>
     <t>LP-053563</t>
   </si>
   <si>
     <t>LP-053565</t>
   </si>
   <si>
-    <t>LP-053717</t>
-  </si>
-  <si>
-    <t>LP-053796</t>
-  </si>
-  <si>
-    <t>LP-053898</t>
-  </si>
-  <si>
-    <t>LP-053904</t>
-  </si>
-  <si>
-    <t>LP-053930</t>
-  </si>
-  <si>
-    <t>LP-053942</t>
-  </si>
-  <si>
     <t>LP-053949</t>
   </si>
   <si>
@@ -376,154 +122,10 @@
     <t>LP-053953</t>
   </si>
   <si>
-    <t>LP-054181</t>
-  </si>
-  <si>
-    <t>LP-054183</t>
+    <t>LP-054186</t>
   </si>
   <si>
     <t>LP-054188</t>
-  </si>
-  <si>
-    <t>LP-054349</t>
-  </si>
-  <si>
-    <t>LP-054393</t>
-  </si>
-  <si>
-    <t>LP-054549</t>
-  </si>
-  <si>
-    <t>LP-054550</t>
-  </si>
-  <si>
-    <t>LP-054551</t>
-  </si>
-  <si>
-    <t>LP-054553</t>
-  </si>
-  <si>
-    <t>LP-054581</t>
-  </si>
-  <si>
-    <t>LP-054623</t>
-  </si>
-  <si>
-    <t>LP-048367</t>
-  </si>
-  <si>
-    <t>LP-050448</t>
-  </si>
-  <si>
-    <t>LP-051075</t>
-  </si>
-  <si>
-    <t>LP-052398</t>
-  </si>
-  <si>
-    <t>LP-053210</t>
-  </si>
-  <si>
-    <t>LP-053239</t>
-  </si>
-  <si>
-    <t>LP-053253</t>
-  </si>
-  <si>
-    <t>LP-053903</t>
-  </si>
-  <si>
-    <t>LP-053915</t>
-  </si>
-  <si>
-    <t>LP-054186</t>
-  </si>
-  <si>
-    <t>LP-054211</t>
-  </si>
-  <si>
-    <t>LP-054552</t>
-  </si>
-  <si>
-    <t>LP-047971</t>
-  </si>
-  <si>
-    <t>LP-049433</t>
-  </si>
-  <si>
-    <t>LP-052888</t>
-  </si>
-  <si>
-    <t>LP-052389</t>
-  </si>
-  <si>
-    <t>LP-053192</t>
-  </si>
-  <si>
-    <t>LP-053530</t>
-  </si>
-  <si>
-    <t>LP-053531</t>
-  </si>
-  <si>
-    <t>LP-053532</t>
-  </si>
-  <si>
-    <t>LP-053566</t>
-  </si>
-  <si>
-    <t>LP-053630</t>
-  </si>
-  <si>
-    <t>LP-053660</t>
-  </si>
-  <si>
-    <t>LP-053729</t>
-  </si>
-  <si>
-    <t>LP-053809</t>
-  </si>
-  <si>
-    <t>LP-053829</t>
-  </si>
-  <si>
-    <t>LP-053848</t>
-  </si>
-  <si>
-    <t>LP-053850</t>
-  </si>
-  <si>
-    <t>LP-053918</t>
-  </si>
-  <si>
-    <t>LP-053923</t>
-  </si>
-  <si>
-    <t>LP-053924</t>
-  </si>
-  <si>
-    <t>LP-053966</t>
-  </si>
-  <si>
-    <t>LP-054061</t>
-  </si>
-  <si>
-    <t>LP-054073</t>
-  </si>
-  <si>
-    <t>LP-054077</t>
-  </si>
-  <si>
-    <t>LP-054078</t>
-  </si>
-  <si>
-    <t>LP-054080</t>
-  </si>
-  <si>
-    <t>LP-054089</t>
-  </si>
-  <si>
-    <t>LP-054099</t>
   </si>
   <si>
     <t>LP-054120</t>
@@ -1133,18 +735,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1155,7 +752,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1163,30 +760,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1489,974 +1068,1052 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B230"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>137</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
@@ -2649,702 +2306,8 @@
         <v>230</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A267" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A268" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A269" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A270" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A274" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A275" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A286" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A322" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A324" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A325" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A326" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A327" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A329" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A330" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A331" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A332" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A333" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A336" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A338" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A339" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A340" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A341" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A342" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A344" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A345" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A347" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A356" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A357" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A358" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A359" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A360" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A361" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A362" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A363" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A364" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A365" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A366" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A367" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A368" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
-        <v>367</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:B230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/99 - Excels/Open-LPs.xlsx
+++ b/99 - Excels/Open-LPs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CF322F-EA3D-4C77-9480-168525F66EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543831AC-4B8B-4C85-B187-E2338994A78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$221</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="222">
   <si>
     <t>LP</t>
   </si>
@@ -126,33 +126,6 @@
   </si>
   <si>
     <t>LP-054188</t>
-  </si>
-  <si>
-    <t>LP-054120</t>
-  </si>
-  <si>
-    <t>LP-054121</t>
-  </si>
-  <si>
-    <t>LP-054124</t>
-  </si>
-  <si>
-    <t>LP-054127</t>
-  </si>
-  <si>
-    <t>LP-054145</t>
-  </si>
-  <si>
-    <t>LP-054147</t>
-  </si>
-  <si>
-    <t>LP-054148</t>
-  </si>
-  <si>
-    <t>LP-054149</t>
-  </si>
-  <si>
-    <t>LP-054150</t>
   </si>
   <si>
     <t>LP-054155</t>
@@ -1068,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B230"/>
+  <dimension ref="A1:B221"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1748,52 +1721,52 @@
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>121</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>3</v>
+        <v>129</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
@@ -2073,47 +2046,47 @@
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
@@ -2261,53 +2234,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>230</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/99 - Excels/Open-LPs.xlsx
+++ b/99 - Excels/Open-LPs.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apropriado</t>
+          <t>Encerrado</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apropriado</t>
+          <t>Error</t>
         </is>
       </c>
     </row>

--- a/99 - Excels/Open-LPs.xlsx
+++ b/99 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2AB3A0-59E7-45E1-B4B6-5BD4C9B53E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452DB745-701F-487A-BA2F-74FC4CC402A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="1025">
   <si>
     <t>LP</t>
   </si>
@@ -2399,6 +2399,705 @@
   </si>
   <si>
     <t>LP-056278</t>
+  </si>
+  <si>
+    <t>LP-051638</t>
+  </si>
+  <si>
+    <t>LP-053259</t>
+  </si>
+  <si>
+    <t>LP-053292</t>
+  </si>
+  <si>
+    <t>LP-053807</t>
+  </si>
+  <si>
+    <t>LP-054590</t>
+  </si>
+  <si>
+    <t>LP-054740</t>
+  </si>
+  <si>
+    <t>LP-054930</t>
+  </si>
+  <si>
+    <t>LP-054955</t>
+  </si>
+  <si>
+    <t>LP-054980</t>
+  </si>
+  <si>
+    <t>LP-054981</t>
+  </si>
+  <si>
+    <t>LP-055047</t>
+  </si>
+  <si>
+    <t>LP-055088</t>
+  </si>
+  <si>
+    <t>LP-055097</t>
+  </si>
+  <si>
+    <t>LP-055148</t>
+  </si>
+  <si>
+    <t>LP-055156</t>
+  </si>
+  <si>
+    <t>LP-055158</t>
+  </si>
+  <si>
+    <t>LP-055164</t>
+  </si>
+  <si>
+    <t>LP-055180</t>
+  </si>
+  <si>
+    <t>LP-055230</t>
+  </si>
+  <si>
+    <t>LP-055260</t>
+  </si>
+  <si>
+    <t>LP-055369</t>
+  </si>
+  <si>
+    <t>LP-055371</t>
+  </si>
+  <si>
+    <t>LP-055394</t>
+  </si>
+  <si>
+    <t>LP-055395</t>
+  </si>
+  <si>
+    <t>LP-055415</t>
+  </si>
+  <si>
+    <t>LP-055427</t>
+  </si>
+  <si>
+    <t>LP-055433</t>
+  </si>
+  <si>
+    <t>LP-055518</t>
+  </si>
+  <si>
+    <t>LP-055523</t>
+  </si>
+  <si>
+    <t>LP-055537</t>
+  </si>
+  <si>
+    <t>LP-055540</t>
+  </si>
+  <si>
+    <t>LP-055551</t>
+  </si>
+  <si>
+    <t>LP-055554</t>
+  </si>
+  <si>
+    <t>LP-055570</t>
+  </si>
+  <si>
+    <t>LP-055575</t>
+  </si>
+  <si>
+    <t>LP-055576</t>
+  </si>
+  <si>
+    <t>LP-055580</t>
+  </si>
+  <si>
+    <t>LP-055604</t>
+  </si>
+  <si>
+    <t>LP-055606</t>
+  </si>
+  <si>
+    <t>LP-055607</t>
+  </si>
+  <si>
+    <t>LP-055623</t>
+  </si>
+  <si>
+    <t>LP-055629</t>
+  </si>
+  <si>
+    <t>LP-055654</t>
+  </si>
+  <si>
+    <t>LP-055721</t>
+  </si>
+  <si>
+    <t>LP-055730</t>
+  </si>
+  <si>
+    <t>LP-055731</t>
+  </si>
+  <si>
+    <t>LP-055749</t>
+  </si>
+  <si>
+    <t>LP-055777</t>
+  </si>
+  <si>
+    <t>LP-055814</t>
+  </si>
+  <si>
+    <t>LP-055865</t>
+  </si>
+  <si>
+    <t>LP-055907</t>
+  </si>
+  <si>
+    <t>LP-055909</t>
+  </si>
+  <si>
+    <t>LP-055911</t>
+  </si>
+  <si>
+    <t>LP-055917</t>
+  </si>
+  <si>
+    <t>LP-055918</t>
+  </si>
+  <si>
+    <t>LP-055924</t>
+  </si>
+  <si>
+    <t>LP-055925</t>
+  </si>
+  <si>
+    <t>LP-055926</t>
+  </si>
+  <si>
+    <t>LP-055936</t>
+  </si>
+  <si>
+    <t>LP-056063</t>
+  </si>
+  <si>
+    <t>LP-056072</t>
+  </si>
+  <si>
+    <t>LP-056073</t>
+  </si>
+  <si>
+    <t>LP-056078</t>
+  </si>
+  <si>
+    <t>LP-056079</t>
+  </si>
+  <si>
+    <t>LP-056097</t>
+  </si>
+  <si>
+    <t>LP-050245</t>
+  </si>
+  <si>
+    <t>LP-050251</t>
+  </si>
+  <si>
+    <t>LP-050761</t>
+  </si>
+  <si>
+    <t>LP-050781</t>
+  </si>
+  <si>
+    <t>LP-051027</t>
+  </si>
+  <si>
+    <t>LP-051031</t>
+  </si>
+  <si>
+    <t>LP-051034</t>
+  </si>
+  <si>
+    <t>LP-051035</t>
+  </si>
+  <si>
+    <t>LP-051046</t>
+  </si>
+  <si>
+    <t>LP-051054</t>
+  </si>
+  <si>
+    <t>LP-051079</t>
+  </si>
+  <si>
+    <t>LP-051141</t>
+  </si>
+  <si>
+    <t>LP-051152</t>
+  </si>
+  <si>
+    <t>LP-051153</t>
+  </si>
+  <si>
+    <t>LP-051154</t>
+  </si>
+  <si>
+    <t>LP-052100</t>
+  </si>
+  <si>
+    <t>LP-052101</t>
+  </si>
+  <si>
+    <t>LP-052237</t>
+  </si>
+  <si>
+    <t>LP-052244</t>
+  </si>
+  <si>
+    <t>LP-052377</t>
+  </si>
+  <si>
+    <t>LP-052406</t>
+  </si>
+  <si>
+    <t>LP-052627</t>
+  </si>
+  <si>
+    <t>LP-052677</t>
+  </si>
+  <si>
+    <t>LP-052705</t>
+  </si>
+  <si>
+    <t>LP-052706</t>
+  </si>
+  <si>
+    <t>LP-052708</t>
+  </si>
+  <si>
+    <t>LP-052710</t>
+  </si>
+  <si>
+    <t>LP-052711</t>
+  </si>
+  <si>
+    <t>LP-052744</t>
+  </si>
+  <si>
+    <t>LP-052791</t>
+  </si>
+  <si>
+    <t>LP-052915</t>
+  </si>
+  <si>
+    <t>LP-052919</t>
+  </si>
+  <si>
+    <t>LP-052921</t>
+  </si>
+  <si>
+    <t>LP-052957</t>
+  </si>
+  <si>
+    <t>LP-053023</t>
+  </si>
+  <si>
+    <t>LP-053025</t>
+  </si>
+  <si>
+    <t>LP-053052</t>
+  </si>
+  <si>
+    <t>LP-053055</t>
+  </si>
+  <si>
+    <t>LP-053107</t>
+  </si>
+  <si>
+    <t>LP-053110</t>
+  </si>
+  <si>
+    <t>LP-053211</t>
+  </si>
+  <si>
+    <t>LP-053229</t>
+  </si>
+  <si>
+    <t>LP-053299</t>
+  </si>
+  <si>
+    <t>LP-053397</t>
+  </si>
+  <si>
+    <t>LP-053403</t>
+  </si>
+  <si>
+    <t>LP-053406</t>
+  </si>
+  <si>
+    <t>LP-053411</t>
+  </si>
+  <si>
+    <t>LP-053412</t>
+  </si>
+  <si>
+    <t>LP-053414</t>
+  </si>
+  <si>
+    <t>LP-053415</t>
+  </si>
+  <si>
+    <t>LP-053423</t>
+  </si>
+  <si>
+    <t>LP-053424</t>
+  </si>
+  <si>
+    <t>LP-053425</t>
+  </si>
+  <si>
+    <t>LP-053427</t>
+  </si>
+  <si>
+    <t>LP-053429</t>
+  </si>
+  <si>
+    <t>LP-053444</t>
+  </si>
+  <si>
+    <t>LP-053445</t>
+  </si>
+  <si>
+    <t>LP-053508</t>
+  </si>
+  <si>
+    <t>LP-053804</t>
+  </si>
+  <si>
+    <t>LP-053883</t>
+  </si>
+  <si>
+    <t>LP-053893</t>
+  </si>
+  <si>
+    <t>LP-053944</t>
+  </si>
+  <si>
+    <t>LP-053945</t>
+  </si>
+  <si>
+    <t>LP-054173</t>
+  </si>
+  <si>
+    <t>LP-054174</t>
+  </si>
+  <si>
+    <t>LP-054187</t>
+  </si>
+  <si>
+    <t>LP-054204</t>
+  </si>
+  <si>
+    <t>LP-054356</t>
+  </si>
+  <si>
+    <t>LP-054555</t>
+  </si>
+  <si>
+    <t>LP-054564</t>
+  </si>
+  <si>
+    <t>LP-054573</t>
+  </si>
+  <si>
+    <t>LP-054733</t>
+  </si>
+  <si>
+    <t>LP-054735</t>
+  </si>
+  <si>
+    <t>LP-054826</t>
+  </si>
+  <si>
+    <t>LP-054835</t>
+  </si>
+  <si>
+    <t>LP-054836</t>
+  </si>
+  <si>
+    <t>LP-054905</t>
+  </si>
+  <si>
+    <t>LP-054906</t>
+  </si>
+  <si>
+    <t>LP-054908</t>
+  </si>
+  <si>
+    <t>LP-054909</t>
+  </si>
+  <si>
+    <t>LP-054959</t>
+  </si>
+  <si>
+    <t>LP-054961</t>
+  </si>
+  <si>
+    <t>LP-055068</t>
+  </si>
+  <si>
+    <t>LP-055069</t>
+  </si>
+  <si>
+    <t>LP-055077</t>
+  </si>
+  <si>
+    <t>LP-055078</t>
+  </si>
+  <si>
+    <t>LP-055081</t>
+  </si>
+  <si>
+    <t>LP-055082</t>
+  </si>
+  <si>
+    <t>LP-055165</t>
+  </si>
+  <si>
+    <t>LP-055321</t>
+  </si>
+  <si>
+    <t>LP-055322</t>
+  </si>
+  <si>
+    <t>LP-055366</t>
+  </si>
+  <si>
+    <t>LP-055336</t>
+  </si>
+  <si>
+    <t>LP-055344</t>
+  </si>
+  <si>
+    <t>LP-055363</t>
+  </si>
+  <si>
+    <t>LP-055370</t>
+  </si>
+  <si>
+    <t>LP-055373</t>
+  </si>
+  <si>
+    <t>LP-055376</t>
+  </si>
+  <si>
+    <t>LP-055398</t>
+  </si>
+  <si>
+    <t>LP-055499</t>
+  </si>
+  <si>
+    <t>LP-055641</t>
+  </si>
+  <si>
+    <t>LP-055662</t>
+  </si>
+  <si>
+    <t>LP-055664</t>
+  </si>
+  <si>
+    <t>LP-055666</t>
+  </si>
+  <si>
+    <t>LP-055668</t>
+  </si>
+  <si>
+    <t>LP-055669</t>
+  </si>
+  <si>
+    <t>LP-055671</t>
+  </si>
+  <si>
+    <t>LP-055677</t>
+  </si>
+  <si>
+    <t>LP-055679</t>
+  </si>
+  <si>
+    <t>LP-055686</t>
+  </si>
+  <si>
+    <t>LP-055695</t>
+  </si>
+  <si>
+    <t>LP-055704</t>
+  </si>
+  <si>
+    <t>LP-055705</t>
+  </si>
+  <si>
+    <t>LP-055706</t>
+  </si>
+  <si>
+    <t>LP-055707</t>
+  </si>
+  <si>
+    <t>LP-055708</t>
+  </si>
+  <si>
+    <t>LP-055709</t>
+  </si>
+  <si>
+    <t>LP-055733</t>
+  </si>
+  <si>
+    <t>LP-055734</t>
+  </si>
+  <si>
+    <t>LP-055735</t>
+  </si>
+  <si>
+    <t>LP-055758</t>
+  </si>
+  <si>
+    <t>LP-055766</t>
+  </si>
+  <si>
+    <t>LP-055798</t>
+  </si>
+  <si>
+    <t>LP-055806</t>
+  </si>
+  <si>
+    <t>LP-055839</t>
+  </si>
+  <si>
+    <t>LP-055840</t>
+  </si>
+  <si>
+    <t>LP-055950</t>
+  </si>
+  <si>
+    <t>LP-056039</t>
+  </si>
+  <si>
+    <t>LP-056041</t>
+  </si>
+  <si>
+    <t>LP-056050</t>
+  </si>
+  <si>
+    <t>LP-056052</t>
+  </si>
+  <si>
+    <t>LP-056054</t>
+  </si>
+  <si>
+    <t>LP-056056</t>
+  </si>
+  <si>
+    <t>LP-056081</t>
+  </si>
+  <si>
+    <t>LP-056082</t>
+  </si>
+  <si>
+    <t>LP-056084</t>
+  </si>
+  <si>
+    <t>LP-056085</t>
+  </si>
+  <si>
+    <t>LP-056086</t>
+  </si>
+  <si>
+    <t>LP-056087</t>
+  </si>
+  <si>
+    <t>LP-056088</t>
+  </si>
+  <si>
+    <t>LP-056116</t>
+  </si>
+  <si>
+    <t>LP-056121</t>
+  </si>
+  <si>
+    <t>LP-056127</t>
+  </si>
+  <si>
+    <t>LP-056128</t>
+  </si>
+  <si>
+    <t>LP-056134</t>
+  </si>
+  <si>
+    <t>LP-056136</t>
+  </si>
+  <si>
+    <t>LP-056200</t>
+  </si>
+  <si>
+    <t>LP-056282</t>
+  </si>
+  <si>
+    <t>LP-056372</t>
+  </si>
+  <si>
+    <t>LP-056373</t>
+  </si>
+  <si>
+    <t>LP-056378</t>
+  </si>
+  <si>
+    <t>LP-056379</t>
+  </si>
+  <si>
+    <t>LP-056386</t>
+  </si>
+  <si>
+    <t>LP-056387</t>
+  </si>
+  <si>
+    <t>LP-056389</t>
+  </si>
+  <si>
+    <t>LP-056390</t>
+  </si>
+  <si>
+    <t>LP-056404</t>
+  </si>
+  <si>
+    <t>LP-056405</t>
+  </si>
+  <si>
+    <t>LP-056407</t>
+  </si>
+  <si>
+    <t>LP-056408</t>
+  </si>
+  <si>
+    <t>LP-056409</t>
+  </si>
+  <si>
+    <t>LP-056415</t>
+  </si>
+  <si>
+    <t>LP-056453</t>
+  </si>
+  <si>
+    <t>LP-056523</t>
+  </si>
+  <si>
+    <t>LP-056624</t>
+  </si>
+  <si>
+    <t>LP-056625</t>
+  </si>
+  <si>
+    <t>LP-056715</t>
+  </si>
+  <si>
+    <t>LP-056718</t>
   </si>
 </sst>
 </file>
@@ -2738,7 +3437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B794"/>
+  <dimension ref="A1:B1028"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -6718,6 +7417,1176 @@
         <v>791</v>
       </c>
     </row>
+    <row r="795" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A795" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="796" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A796" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="797" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A797" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="798" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A798" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="799" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A799" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="800" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A800" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="801" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A801" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="802" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A802" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="803" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A803" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="804" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A804" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="805" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A805" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="806" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A806" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="807" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A807" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="808" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A808" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="809" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A809" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="810" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A810" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="811" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="812" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="813" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A813" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="814" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A814" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="815" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A815" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="816" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A816" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="817" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A817" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="818" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A818" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="819" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A819" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="820" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A820" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="821" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A821" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="822" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A822" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="823" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A823" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="824" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A824" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="825" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A825" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="826" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A826" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="827" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A827" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="828" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A828" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="829" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A829" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="830" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A830" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="831" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A831" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="832" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A832" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="833" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A833" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="834" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A834" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="835" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A835" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="836" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A836" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="837" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A837" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="838" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A838" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="839" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A839" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="840" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A840" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="841" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A841" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="842" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A842" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="843" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A843" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="844" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A844" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="845" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A845" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="846" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A846" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="847" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A847" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="848" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A848" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="849" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A849" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="850" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A850" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="851" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A851" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="852" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A852" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="853" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A853" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="854" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A854" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="855" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A855" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="856" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A856" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="857" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A857" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="858" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A858" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="859" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A859" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="860" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A860" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="861" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A861" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="862" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A862" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="863" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A863" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="864" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A864" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="865" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A865" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="866" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A866" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="867" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A867" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="868" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A868" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="869" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A869" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="870" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A870" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="871" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A871" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="872" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A872" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="873" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A873" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="874" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A874" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="875" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A875" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="876" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A876" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="877" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A877" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="878" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A878" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="879" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A879" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="880" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A880" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="881" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A881" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="882" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A882" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="883" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A883" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="884" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A884" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="885" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A885" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="886" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A886" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="887" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A887" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="888" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A888" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="889" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A889" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="890" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A890" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="891" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A891" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="892" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A892" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="893" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A893" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="894" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A894" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="895" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A895" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="896" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A896" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="897" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A897" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="898" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A898" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="899" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A899" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="900" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A900" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="901" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A901" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="902" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A902" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="903" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A903" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="904" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A904" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="905" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A905" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="906" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A906" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="907" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A907" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="908" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A908" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="909" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A909" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="910" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A910" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="911" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A911" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="912" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A912" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="913" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A913" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="914" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A914" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="915" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A915" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="916" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A916" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="917" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A917" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="918" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A918" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="919" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A919" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="920" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A920" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="921" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A921" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="922" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A922" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="923" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A923" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="924" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A924" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="925" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A925" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="926" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A926" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="927" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A927" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="928" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A928" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="929" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A929" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="930" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A930" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="931" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A931" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="932" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A932" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="933" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A933" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="934" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A934" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="935" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A935" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="936" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A936" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="937" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A937" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="938" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A938" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="939" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A939" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="940" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A940" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="941" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A941" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="942" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A942" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="943" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A943" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="944" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A944" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="945" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A945" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="946" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A946" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="947" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A947" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="948" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A948" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="949" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A949" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="950" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A950" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="951" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A951" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="952" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A952" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="953" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A953" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="954" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A954" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="955" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A955" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="956" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A956" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="957" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A957" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="958" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A958" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="959" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A959" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="960" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A960" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="961" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A961" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="962" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A962" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="963" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A963" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="964" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A964" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="965" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A965" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="966" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A966" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="967" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A967" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="968" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A968" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="969" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A969" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="970" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A970" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="971" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A971" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="972" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A972" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="973" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A973" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="974" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A974" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="975" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A975" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="976" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A976" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="977" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A977" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="978" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A978" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="979" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A979" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="980" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A980" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="981" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A981" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="982" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A982" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="983" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A983" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="984" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A984" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="985" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A985" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="986" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A986" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="987" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A987" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="988" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A988" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="989" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A989" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="990" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A990" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="991" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A991" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="992" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A992" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="993" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A993" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="994" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A994" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="995" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A995" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="996" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A996" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="997" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A997" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="998" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A998" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="999" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A999" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1000" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1001" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1002" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1003" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1004" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1005" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1006" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1007" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1008" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1009" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1010" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1011" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1012" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1013" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1014" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1015" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1016" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1017" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1018" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1019" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1020" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1021" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1022" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1023" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1024" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1025" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1026" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1027" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1028" t="s">
+        <v>1024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/99 - Excels/Open-LPs.xlsx
+++ b/99 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452DB745-701F-487A-BA2F-74FC4CC402A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D638AB-03F9-420D-952F-D31ECD0F3B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="1365">
   <si>
     <t>LP</t>
   </si>
@@ -3098,6 +3098,1026 @@
   </si>
   <si>
     <t>LP-056718</t>
+  </si>
+  <si>
+    <t>LP-057268</t>
+  </si>
+  <si>
+    <t>LP-057243</t>
+  </si>
+  <si>
+    <t>LP-057223</t>
+  </si>
+  <si>
+    <t>LP-057143</t>
+  </si>
+  <si>
+    <t>LP-057095</t>
+  </si>
+  <si>
+    <t>LP-057071</t>
+  </si>
+  <si>
+    <t>LP-057070</t>
+  </si>
+  <si>
+    <t>LP-057055</t>
+  </si>
+  <si>
+    <t>LP-057054</t>
+  </si>
+  <si>
+    <t>LP-057036</t>
+  </si>
+  <si>
+    <t>LP-057032</t>
+  </si>
+  <si>
+    <t>LP-057031</t>
+  </si>
+  <si>
+    <t>LP-057030</t>
+  </si>
+  <si>
+    <t>LP-057023</t>
+  </si>
+  <si>
+    <t>LP-056998</t>
+  </si>
+  <si>
+    <t>LP-056941</t>
+  </si>
+  <si>
+    <t>LP-056894</t>
+  </si>
+  <si>
+    <t>LP-056892</t>
+  </si>
+  <si>
+    <t>LP-056880</t>
+  </si>
+  <si>
+    <t>LP-056874</t>
+  </si>
+  <si>
+    <t>LP-056867</t>
+  </si>
+  <si>
+    <t>LP-056828</t>
+  </si>
+  <si>
+    <t>LP-056780</t>
+  </si>
+  <si>
+    <t>LP-056762</t>
+  </si>
+  <si>
+    <t>LP-056730</t>
+  </si>
+  <si>
+    <t>LP-056727</t>
+  </si>
+  <si>
+    <t>LP-056664</t>
+  </si>
+  <si>
+    <t>LP-056663</t>
+  </si>
+  <si>
+    <t>LP-056627</t>
+  </si>
+  <si>
+    <t>LP-056568</t>
+  </si>
+  <si>
+    <t>LP-056551</t>
+  </si>
+  <si>
+    <t>LP-056482</t>
+  </si>
+  <si>
+    <t>LP-056473</t>
+  </si>
+  <si>
+    <t>LP-056472</t>
+  </si>
+  <si>
+    <t>LP-056471</t>
+  </si>
+  <si>
+    <t>LP-056385</t>
+  </si>
+  <si>
+    <t>LP-056316</t>
+  </si>
+  <si>
+    <t>LP-056313</t>
+  </si>
+  <si>
+    <t>LP-056309</t>
+  </si>
+  <si>
+    <t>LP-056292</t>
+  </si>
+  <si>
+    <t>LP-056267</t>
+  </si>
+  <si>
+    <t>LP-056259</t>
+  </si>
+  <si>
+    <t>LP-056241</t>
+  </si>
+  <si>
+    <t>LP-056239</t>
+  </si>
+  <si>
+    <t>LP-056238</t>
+  </si>
+  <si>
+    <t>LP-056237</t>
+  </si>
+  <si>
+    <t>LP-056236</t>
+  </si>
+  <si>
+    <t>LP-056235</t>
+  </si>
+  <si>
+    <t>LP-056230</t>
+  </si>
+  <si>
+    <t>LP-056179</t>
+  </si>
+  <si>
+    <t>LP-056177</t>
+  </si>
+  <si>
+    <t>LP-056105</t>
+  </si>
+  <si>
+    <t>LP-056080</t>
+  </si>
+  <si>
+    <t>LP-056076</t>
+  </si>
+  <si>
+    <t>LP-056065</t>
+  </si>
+  <si>
+    <t>LP-056062</t>
+  </si>
+  <si>
+    <t>LP-056059</t>
+  </si>
+  <si>
+    <t>LP-055935</t>
+  </si>
+  <si>
+    <t>LP-055923</t>
+  </si>
+  <si>
+    <t>LP-055922</t>
+  </si>
+  <si>
+    <t>LP-055921</t>
+  </si>
+  <si>
+    <t>LP-055920</t>
+  </si>
+  <si>
+    <t>LP-055919</t>
+  </si>
+  <si>
+    <t>LP-055902</t>
+  </si>
+  <si>
+    <t>LP-055881</t>
+  </si>
+  <si>
+    <t>LP-055830</t>
+  </si>
+  <si>
+    <t>LP-055828</t>
+  </si>
+  <si>
+    <t>LP-055826</t>
+  </si>
+  <si>
+    <t>LP-055825</t>
+  </si>
+  <si>
+    <t>LP-055822</t>
+  </si>
+  <si>
+    <t>LP-055804</t>
+  </si>
+  <si>
+    <t>LP-055795</t>
+  </si>
+  <si>
+    <t>LP-055790</t>
+  </si>
+  <si>
+    <t>LP-055742</t>
+  </si>
+  <si>
+    <t>LP-055741</t>
+  </si>
+  <si>
+    <t>LP-055713</t>
+  </si>
+  <si>
+    <t>LP-055688</t>
+  </si>
+  <si>
+    <t>LP-055687</t>
+  </si>
+  <si>
+    <t>LP-055663</t>
+  </si>
+  <si>
+    <t>LP-055631</t>
+  </si>
+  <si>
+    <t>LP-055618</t>
+  </si>
+  <si>
+    <t>LP-055617</t>
+  </si>
+  <si>
+    <t>LP-056098</t>
+  </si>
+  <si>
+    <t>LP-056101</t>
+  </si>
+  <si>
+    <t>LP-056112</t>
+  </si>
+  <si>
+    <t>LP-056114</t>
+  </si>
+  <si>
+    <t>LP-056144</t>
+  </si>
+  <si>
+    <t>LP-056145</t>
+  </si>
+  <si>
+    <t>LP-056158</t>
+  </si>
+  <si>
+    <t>LP-056161</t>
+  </si>
+  <si>
+    <t>LP-056175</t>
+  </si>
+  <si>
+    <t>LP-056182</t>
+  </si>
+  <si>
+    <t>LP-056183</t>
+  </si>
+  <si>
+    <t>LP-056185</t>
+  </si>
+  <si>
+    <t>LP-056186</t>
+  </si>
+  <si>
+    <t>LP-056187</t>
+  </si>
+  <si>
+    <t>LP-056188</t>
+  </si>
+  <si>
+    <t>LP-056189</t>
+  </si>
+  <si>
+    <t>LP-056190</t>
+  </si>
+  <si>
+    <t>LP-056191</t>
+  </si>
+  <si>
+    <t>LP-056193</t>
+  </si>
+  <si>
+    <t>LP-056194</t>
+  </si>
+  <si>
+    <t>LP-056211</t>
+  </si>
+  <si>
+    <t>LP-056214</t>
+  </si>
+  <si>
+    <t>LP-056216</t>
+  </si>
+  <si>
+    <t>LP-056240</t>
+  </si>
+  <si>
+    <t>LP-056242</t>
+  </si>
+  <si>
+    <t>LP-056251</t>
+  </si>
+  <si>
+    <t>LP-056253</t>
+  </si>
+  <si>
+    <t>LP-056258</t>
+  </si>
+  <si>
+    <t>LP-056260</t>
+  </si>
+  <si>
+    <t>LP-056264</t>
+  </si>
+  <si>
+    <t>LP-056268</t>
+  </si>
+  <si>
+    <t>LP-056269</t>
+  </si>
+  <si>
+    <t>LP-056283</t>
+  </si>
+  <si>
+    <t>LP-056285</t>
+  </si>
+  <si>
+    <t>LP-056290</t>
+  </si>
+  <si>
+    <t>LP-056294</t>
+  </si>
+  <si>
+    <t>LP-056295</t>
+  </si>
+  <si>
+    <t>LP-056340</t>
+  </si>
+  <si>
+    <t>LP-056342</t>
+  </si>
+  <si>
+    <t>LP-056428</t>
+  </si>
+  <si>
+    <t>LP-056445</t>
+  </si>
+  <si>
+    <t>LP-056447</t>
+  </si>
+  <si>
+    <t>LP-056448</t>
+  </si>
+  <si>
+    <t>LP-056449</t>
+  </si>
+  <si>
+    <t>LP-056457</t>
+  </si>
+  <si>
+    <t>LP-056461</t>
+  </si>
+  <si>
+    <t>LP-056561</t>
+  </si>
+  <si>
+    <t>LP-056583</t>
+  </si>
+  <si>
+    <t>LP-056626</t>
+  </si>
+  <si>
+    <t>LP-055645</t>
+  </si>
+  <si>
+    <t>LP-056699</t>
+  </si>
+  <si>
+    <t>LP-056704</t>
+  </si>
+  <si>
+    <t>LP-056709</t>
+  </si>
+  <si>
+    <t>LP-056723</t>
+  </si>
+  <si>
+    <t>LP-056724</t>
+  </si>
+  <si>
+    <t>LP-056734</t>
+  </si>
+  <si>
+    <t>LP-056735</t>
+  </si>
+  <si>
+    <t>LP-056866</t>
+  </si>
+  <si>
+    <t>LP-056937</t>
+  </si>
+  <si>
+    <t>LP-056940</t>
+  </si>
+  <si>
+    <t>LP-057178</t>
+  </si>
+  <si>
+    <t>LP-057194</t>
+  </si>
+  <si>
+    <t>LP-057203</t>
+  </si>
+  <si>
+    <t>LP-057302</t>
+  </si>
+  <si>
+    <t>LP-057312</t>
+  </si>
+  <si>
+    <t>LP-057313</t>
+  </si>
+  <si>
+    <t>LP-057360</t>
+  </si>
+  <si>
+    <t>LP-057402</t>
+  </si>
+  <si>
+    <t>LP-056528</t>
+  </si>
+  <si>
+    <t>LP-056495</t>
+  </si>
+  <si>
+    <t>LP-056414</t>
+  </si>
+  <si>
+    <t>LP-056406</t>
+  </si>
+  <si>
+    <t>LP-056402</t>
+  </si>
+  <si>
+    <t>LP-056401</t>
+  </si>
+  <si>
+    <t>LP-056374</t>
+  </si>
+  <si>
+    <t>LP-056226</t>
+  </si>
+  <si>
+    <t>LP-056043</t>
+  </si>
+  <si>
+    <t>LP-056042</t>
+  </si>
+  <si>
+    <t>LP-055952</t>
+  </si>
+  <si>
+    <t>LP-055842</t>
+  </si>
+  <si>
+    <t>LP-055723</t>
+  </si>
+  <si>
+    <t>LP-055684</t>
+  </si>
+  <si>
+    <t>LP-055382</t>
+  </si>
+  <si>
+    <t>LP-055673</t>
+  </si>
+  <si>
+    <t>LP-055672</t>
+  </si>
+  <si>
+    <t>LP-055660</t>
+  </si>
+  <si>
+    <t>LP-055659</t>
+  </si>
+  <si>
+    <t>LP-055345</t>
+  </si>
+  <si>
+    <t>LP-054464</t>
+  </si>
+  <si>
+    <t>LP-055198</t>
+  </si>
+  <si>
+    <t>LP-055080</t>
+  </si>
+  <si>
+    <t>LP-054911</t>
+  </si>
+  <si>
+    <t>LP-054833</t>
+  </si>
+  <si>
+    <t>LP-054572</t>
+  </si>
+  <si>
+    <t>LP-053438</t>
+  </si>
+  <si>
+    <t>LP-053413</t>
+  </si>
+  <si>
+    <t>LP-053216</t>
+  </si>
+  <si>
+    <t>LP-053215</t>
+  </si>
+  <si>
+    <t>LP-053104</t>
+  </si>
+  <si>
+    <t>LP-052947</t>
+  </si>
+  <si>
+    <t>LP-052626</t>
+  </si>
+  <si>
+    <t>LP-051803</t>
+  </si>
+  <si>
+    <t>LP-051801</t>
+  </si>
+  <si>
+    <t>LP-051381</t>
+  </si>
+  <si>
+    <t>LP-051703</t>
+  </si>
+  <si>
+    <t>LP-050422</t>
+  </si>
+  <si>
+    <t>LP-049475</t>
+  </si>
+  <si>
+    <t>LP-049096</t>
+  </si>
+  <si>
+    <t>LP-035878</t>
+  </si>
+  <si>
+    <t>LP-047291</t>
+  </si>
+  <si>
+    <t>LP-051493</t>
+  </si>
+  <si>
+    <t>LP-053640</t>
+  </si>
+  <si>
+    <t>LP-053783</t>
+  </si>
+  <si>
+    <t>LP-053881</t>
+  </si>
+  <si>
+    <t>LP-053920</t>
+  </si>
+  <si>
+    <t>LP-054342</t>
+  </si>
+  <si>
+    <t>LP-054381</t>
+  </si>
+  <si>
+    <t>LP-054399</t>
+  </si>
+  <si>
+    <t>LP-054415</t>
+  </si>
+  <si>
+    <t>LP-054428</t>
+  </si>
+  <si>
+    <t>LP-054451</t>
+  </si>
+  <si>
+    <t>LP-054783</t>
+  </si>
+  <si>
+    <t>LP-054897</t>
+  </si>
+  <si>
+    <t>LP-055114</t>
+  </si>
+  <si>
+    <t>LP-055155</t>
+  </si>
+  <si>
+    <t>LP-055329</t>
+  </si>
+  <si>
+    <t>LP-055420</t>
+  </si>
+  <si>
+    <t>LP-055517</t>
+  </si>
+  <si>
+    <t>LP-055536</t>
+  </si>
+  <si>
+    <t>LP-055546</t>
+  </si>
+  <si>
+    <t>LP-055592</t>
+  </si>
+  <si>
+    <t>LP-055605</t>
+  </si>
+  <si>
+    <t>LP-055624</t>
+  </si>
+  <si>
+    <t>LP-055626</t>
+  </si>
+  <si>
+    <t>LP-055640</t>
+  </si>
+  <si>
+    <t>LP-055781</t>
+  </si>
+  <si>
+    <t>LP-055792</t>
+  </si>
+  <si>
+    <t>LP-055820</t>
+  </si>
+  <si>
+    <t>LP-055835</t>
+  </si>
+  <si>
+    <t>LP-055903</t>
+  </si>
+  <si>
+    <t>LP-057012</t>
+  </si>
+  <si>
+    <t>LP-057029</t>
+  </si>
+  <si>
+    <t>LP-057103</t>
+  </si>
+  <si>
+    <t>LP-057110</t>
+  </si>
+  <si>
+    <t>LP-057124</t>
+  </si>
+  <si>
+    <t>LP-057171</t>
+  </si>
+  <si>
+    <t>LP-057188</t>
+  </si>
+  <si>
+    <t>LP-057189</t>
+  </si>
+  <si>
+    <t>LP-057202</t>
+  </si>
+  <si>
+    <t>LP-057267</t>
+  </si>
+  <si>
+    <t>LP-055613</t>
+  </si>
+  <si>
+    <t>LP-055612</t>
+  </si>
+  <si>
+    <t>LP-055610</t>
+  </si>
+  <si>
+    <t>LP-055609</t>
+  </si>
+  <si>
+    <t>LP-055603</t>
+  </si>
+  <si>
+    <t>LP-055601</t>
+  </si>
+  <si>
+    <t>LP-055599</t>
+  </si>
+  <si>
+    <t>LP-055589</t>
+  </si>
+  <si>
+    <t>LP-055584</t>
+  </si>
+  <si>
+    <t>LP-055556</t>
+  </si>
+  <si>
+    <t>LP-055552</t>
+  </si>
+  <si>
+    <t>LP-055531</t>
+  </si>
+  <si>
+    <t>LP-055530</t>
+  </si>
+  <si>
+    <t>LP-055484</t>
+  </si>
+  <si>
+    <t>LP-055457</t>
+  </si>
+  <si>
+    <t>LP-055441</t>
+  </si>
+  <si>
+    <t>LP-055437</t>
+  </si>
+  <si>
+    <t>LP-055436</t>
+  </si>
+  <si>
+    <t>LP-055416</t>
+  </si>
+  <si>
+    <t>LP-055396</t>
+  </si>
+  <si>
+    <t>LP-055383</t>
+  </si>
+  <si>
+    <t>LP-055161</t>
+  </si>
+  <si>
+    <t>LP-055154</t>
+  </si>
+  <si>
+    <t>LP-055089</t>
+  </si>
+  <si>
+    <t>LP-055085</t>
+  </si>
+  <si>
+    <t>LP-054985</t>
+  </si>
+  <si>
+    <t>LP-054984</t>
+  </si>
+  <si>
+    <t>LP-054954</t>
+  </si>
+  <si>
+    <t>LP-054921</t>
+  </si>
+  <si>
+    <t>LP-054830</t>
+  </si>
+  <si>
+    <t>LP-054791</t>
+  </si>
+  <si>
+    <t>LP-054739</t>
+  </si>
+  <si>
+    <t>LP-054720</t>
+  </si>
+  <si>
+    <t>LP-054639</t>
+  </si>
+  <si>
+    <t>LP-054571</t>
+  </si>
+  <si>
+    <t>LP-054429</t>
+  </si>
+  <si>
+    <t>LP-054375</t>
+  </si>
+  <si>
+    <t>LP-054171</t>
+  </si>
+  <si>
+    <t>LP-054140</t>
+  </si>
+  <si>
+    <t>LP-053855</t>
+  </si>
+  <si>
+    <t>LP-053722</t>
+  </si>
+  <si>
+    <t>LP-053616</t>
+  </si>
+  <si>
+    <t>LP-053433</t>
+  </si>
+  <si>
+    <t>LP-053401</t>
+  </si>
+  <si>
+    <t>LP-053262</t>
+  </si>
+  <si>
+    <t>LP-053111</t>
+  </si>
+  <si>
+    <t>LP-053047</t>
+  </si>
+  <si>
+    <t>LP-053028</t>
+  </si>
+  <si>
+    <t>LP-052982</t>
+  </si>
+  <si>
+    <t>LP-052772</t>
+  </si>
+  <si>
+    <t>LP-052771</t>
+  </si>
+  <si>
+    <t>LP-051039</t>
+  </si>
+  <si>
+    <t>LP-051438</t>
+  </si>
+  <si>
+    <t>LP-050917</t>
+  </si>
+  <si>
+    <t>LP-048180</t>
+  </si>
+  <si>
+    <t>LP-057409</t>
+  </si>
+  <si>
+    <t>LP-057481</t>
+  </si>
+  <si>
+    <t>LP-057582</t>
+  </si>
+  <si>
+    <t>LP-056070</t>
+  </si>
+  <si>
+    <t>LP-056159</t>
+  </si>
+  <si>
+    <t>LP-056198</t>
+  </si>
+  <si>
+    <t>LP-056271</t>
+  </si>
+  <si>
+    <t>LP-056297</t>
+  </si>
+  <si>
+    <t>LP-056330</t>
+  </si>
+  <si>
+    <t>LP-056338</t>
+  </si>
+  <si>
+    <t>LP-056370</t>
+  </si>
+  <si>
+    <t>LP-056417</t>
+  </si>
+  <si>
+    <t>LP-056418</t>
+  </si>
+  <si>
+    <t>LP-056419</t>
+  </si>
+  <si>
+    <t>LP-056425</t>
+  </si>
+  <si>
+    <t>LP-056432</t>
+  </si>
+  <si>
+    <t>LP-056433</t>
+  </si>
+  <si>
+    <t>LP-056434</t>
+  </si>
+  <si>
+    <t>LP-056435</t>
+  </si>
+  <si>
+    <t>LP-056436</t>
+  </si>
+  <si>
+    <t>LP-056437</t>
+  </si>
+  <si>
+    <t>LP-056444</t>
+  </si>
+  <si>
+    <t>LP-056450</t>
+  </si>
+  <si>
+    <t>LP-056456</t>
+  </si>
+  <si>
+    <t>LP-056458</t>
+  </si>
+  <si>
+    <t>LP-056514</t>
+  </si>
+  <si>
+    <t>LP-056559</t>
+  </si>
+  <si>
+    <t>LP-056562</t>
+  </si>
+  <si>
+    <t>LP-056570</t>
+  </si>
+  <si>
+    <t>LP-056571</t>
+  </si>
+  <si>
+    <t>LP-056572</t>
+  </si>
+  <si>
+    <t>LP-056595</t>
+  </si>
+  <si>
+    <t>LP-056702</t>
+  </si>
+  <si>
+    <t>LP-056710</t>
+  </si>
+  <si>
+    <t>LP-056711</t>
+  </si>
+  <si>
+    <t>LP-056712</t>
+  </si>
+  <si>
+    <t>LP-056728</t>
+  </si>
+  <si>
+    <t>LP-056729</t>
+  </si>
+  <si>
+    <t>LP-056732</t>
+  </si>
+  <si>
+    <t>LP-056782</t>
+  </si>
+  <si>
+    <t>LP-056856</t>
+  </si>
+  <si>
+    <t>LP-056862</t>
+  </si>
+  <si>
+    <t>LP-056869</t>
+  </si>
+  <si>
+    <t>LP-056872</t>
+  </si>
+  <si>
+    <t>LP-056873</t>
+  </si>
+  <si>
+    <t>LP-056875</t>
+  </si>
+  <si>
+    <t>LP-056884</t>
+  </si>
+  <si>
+    <t>LP-056885</t>
+  </si>
+  <si>
+    <t>LP-056886</t>
+  </si>
+  <si>
+    <t>LP-056888</t>
+  </si>
+  <si>
+    <t>LP-056925</t>
+  </si>
+  <si>
+    <t>LP-056930</t>
+  </si>
+  <si>
+    <t>LP-056938</t>
   </si>
 </sst>
 </file>
@@ -3437,7 +4457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1028"/>
+  <dimension ref="A1:B1376"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -8587,6 +9607,1746 @@
         <v>1024</v>
       </c>
     </row>
+    <row r="1029" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1029" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1030" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1031" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1032" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1033" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1034" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1035" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1036" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1037" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1038" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1039" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1040" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1041" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1042" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1043" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1044" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1045" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1046" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1047" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1048" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1049" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1050" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1051" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1052" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1053" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1054" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1055" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1056" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1057" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1058" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1059" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1060" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1061" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1062" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1063" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1064" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1065" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1066" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1067" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1068" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1069" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1070" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1071" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1072" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1073" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1074" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1075" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1076" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1077" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1078" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1079" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1080" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1081" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1082" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1083" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1084" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1085" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1086" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1087" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1088" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1089" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1090" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1091" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1092" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1093" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1094" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1095" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1096" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1097" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1098" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1099" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1100" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1101" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1102" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1103" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1104" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1105" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1106" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1107" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1108" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1109" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1110" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1111" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1112" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1113" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1114" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1115" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1116" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1117" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1118" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1119" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1120" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1121" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1122" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1123" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1124" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1125" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1126" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1127" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1128" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1129" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1130" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1131" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1132" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1133" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1134" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1135" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1136" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1137" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1138" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1139" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1140" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1141" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1142" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1143" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1144" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1145" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1146" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1147" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1148" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1149" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1150" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1151" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1152" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1153" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1154" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1155" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1156" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1157" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1158" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1159" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1160" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1161" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1162" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1163" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1164" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1165" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1166" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1167" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1168" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1169" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1170" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1171" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1172" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1173" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1174" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1175" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1176" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1177" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1178" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1179" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1180" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1181" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1182" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1183" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1184" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1185" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1186" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1187" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1188" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1189" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1190" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1191" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1192" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1193" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1194" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1195" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1196" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1197" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1198" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1199" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1200" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1201" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1202" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1203" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1204" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1205" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1206" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1207" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1208" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1209" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1210" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1211" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1212" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1213" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1214" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1215" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1216" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1217" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1218" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1219" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1220" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1221" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1222" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1223" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1224" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1225" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1226" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1227" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1228" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1229" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1230" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1231" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1232" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1233" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1234" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1235" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1236" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1237" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1238" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1239" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1240" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1241" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1242" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1243" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1244" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1245" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1246" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1247" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1248" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1249" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1250" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1251" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1252" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1253" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1254" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1255" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1256" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1257" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1258" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1259" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1260" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1261" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1262" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1263" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1264" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1265" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1266" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1267" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1268" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1269" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1270" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1271" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1272" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1273" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1274" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1275" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1276" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1277" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1278" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1279" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1280" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1281" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1282" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1283" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1284" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1285" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1286" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1287" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1288" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1289" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1290" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1291" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1292" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1293" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1294" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1295" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1296" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1297" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1298" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1299" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1300" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1301" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1302" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1303" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1304" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1305" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1306" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1307" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1308" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1309" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1310" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1311" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1312" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1313" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1314" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1315" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1316" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1317" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1318" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1319" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1320" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1321" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1322" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1323" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1324" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1325" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1326" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1327" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1328" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1329" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1330" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1331" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1332" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1333" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1334" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1335" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1336" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1337" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1338" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1339" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1340" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1341" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1342" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1343" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1344" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1345" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1346" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1347" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1348" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1349" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1350" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1351" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1352" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1353" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1354" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1355" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1356" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1357" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1358" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1359" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1360" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1361" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1362" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1363" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1364" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1365" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1366" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1367" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1368" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1369" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1370" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1371" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1372" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1373" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1374" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1375" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1376" t="s">
+        <v>1364</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/99 - Excels/Open-LPs.xlsx
+++ b/99 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D638AB-03F9-420D-952F-D31ECD0F3B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8870A0AA-4BA2-4013-BA91-D1919544DEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="1365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="1921">
   <si>
     <t>LP</t>
   </si>
@@ -4118,6 +4118,1674 @@
   </si>
   <si>
     <t>LP-056938</t>
+  </si>
+  <si>
+    <t>LP-057164</t>
+  </si>
+  <si>
+    <t>LP-056898</t>
+  </si>
+  <si>
+    <t>LP-056669</t>
+  </si>
+  <si>
+    <t>LP-056574</t>
+  </si>
+  <si>
+    <t>LP-056552</t>
+  </si>
+  <si>
+    <t>LP-056519</t>
+  </si>
+  <si>
+    <t>LP-056487</t>
+  </si>
+  <si>
+    <t>LP-056413</t>
+  </si>
+  <si>
+    <t>LP-056396</t>
+  </si>
+  <si>
+    <t>LP-056395</t>
+  </si>
+  <si>
+    <t>LP-056394</t>
+  </si>
+  <si>
+    <t>LP-056393</t>
+  </si>
+  <si>
+    <t>LP-056327</t>
+  </si>
+  <si>
+    <t>LP-056119</t>
+  </si>
+  <si>
+    <t>LP-056120</t>
+  </si>
+  <si>
+    <t>LP-056006</t>
+  </si>
+  <si>
+    <t>LP-055901</t>
+  </si>
+  <si>
+    <t>LP-055761</t>
+  </si>
+  <si>
+    <t>LP-055747</t>
+  </si>
+  <si>
+    <t>LP-055722</t>
+  </si>
+  <si>
+    <t>LP-055658</t>
+  </si>
+  <si>
+    <t>LP-055651</t>
+  </si>
+  <si>
+    <t>LP-055502</t>
+  </si>
+  <si>
+    <t>LP-055503</t>
+  </si>
+  <si>
+    <t>LP-055381</t>
+  </si>
+  <si>
+    <t>LP-055358</t>
+  </si>
+  <si>
+    <t>LP-055354</t>
+  </si>
+  <si>
+    <t>LP-055353</t>
+  </si>
+  <si>
+    <t>LP-055341</t>
+  </si>
+  <si>
+    <t>LP-055323</t>
+  </si>
+  <si>
+    <t>LP-055075</t>
+  </si>
+  <si>
+    <t>LP-054731</t>
+  </si>
+  <si>
+    <t>LP-054180</t>
+  </si>
+  <si>
+    <t>LP-054179</t>
+  </si>
+  <si>
+    <t>LP-053122</t>
+  </si>
+  <si>
+    <t>LP-052609</t>
+  </si>
+  <si>
+    <t>LP-051214</t>
+  </si>
+  <si>
+    <t>LP-050401</t>
+  </si>
+  <si>
+    <t>LP-049047</t>
+  </si>
+  <si>
+    <t>LP-046045</t>
+  </si>
+  <si>
+    <t>LP-047092</t>
+  </si>
+  <si>
+    <t>LP-053488</t>
+  </si>
+  <si>
+    <t>LP-053808</t>
+  </si>
+  <si>
+    <t>LP-053917</t>
+  </si>
+  <si>
+    <t>LP-054357</t>
+  </si>
+  <si>
+    <t>LP-054475</t>
+  </si>
+  <si>
+    <t>LP-054899</t>
+  </si>
+  <si>
+    <t>LP-054922</t>
+  </si>
+  <si>
+    <t>LP-054925</t>
+  </si>
+  <si>
+    <t>LP-054982</t>
+  </si>
+  <si>
+    <t>LP-055167</t>
+  </si>
+  <si>
+    <t>LP-055168</t>
+  </si>
+  <si>
+    <t>LP-055241</t>
+  </si>
+  <si>
+    <t>LP-055244</t>
+  </si>
+  <si>
+    <t>LP-055315</t>
+  </si>
+  <si>
+    <t>LP-055326</t>
+  </si>
+  <si>
+    <t>LP-055327</t>
+  </si>
+  <si>
+    <t>LP-055328</t>
+  </si>
+  <si>
+    <t>LP-055331</t>
+  </si>
+  <si>
+    <t>LP-055411</t>
+  </si>
+  <si>
+    <t>LP-055483</t>
+  </si>
+  <si>
+    <t>LP-055602</t>
+  </si>
+  <si>
+    <t>LP-055771</t>
+  </si>
+  <si>
+    <t>LP-055779</t>
+  </si>
+  <si>
+    <t>LP-055785</t>
+  </si>
+  <si>
+    <t>LP-055794</t>
+  </si>
+  <si>
+    <t>LP-055797</t>
+  </si>
+  <si>
+    <t>LP-055800</t>
+  </si>
+  <si>
+    <t>LP-055803</t>
+  </si>
+  <si>
+    <t>LP-055815</t>
+  </si>
+  <si>
+    <t>LP-055816</t>
+  </si>
+  <si>
+    <t>LP-055817</t>
+  </si>
+  <si>
+    <t>LP-055821</t>
+  </si>
+  <si>
+    <t>LP-055908</t>
+  </si>
+  <si>
+    <t>LP-055927</t>
+  </si>
+  <si>
+    <t>LP-055939</t>
+  </si>
+  <si>
+    <t>LP-055940</t>
+  </si>
+  <si>
+    <t>LP-056068</t>
+  </si>
+  <si>
+    <t>LP-056094</t>
+  </si>
+  <si>
+    <t>LP-056102</t>
+  </si>
+  <si>
+    <t>LP-056106</t>
+  </si>
+  <si>
+    <t>LP-056113</t>
+  </si>
+  <si>
+    <t>LP-056157</t>
+  </si>
+  <si>
+    <t>LP-056166</t>
+  </si>
+  <si>
+    <t>LP-056215</t>
+  </si>
+  <si>
+    <t>LP-056227</t>
+  </si>
+  <si>
+    <t>LP-056243</t>
+  </si>
+  <si>
+    <t>LP-056256</t>
+  </si>
+  <si>
+    <t>LP-056272</t>
+  </si>
+  <si>
+    <t>LP-056315</t>
+  </si>
+  <si>
+    <t>LP-056329</t>
+  </si>
+  <si>
+    <t>LP-056392</t>
+  </si>
+  <si>
+    <t>LP-056416</t>
+  </si>
+  <si>
+    <t>LP-056545</t>
+  </si>
+  <si>
+    <t>LP-056546</t>
+  </si>
+  <si>
+    <t>LP-056569</t>
+  </si>
+  <si>
+    <t>LP-056649</t>
+  </si>
+  <si>
+    <t>LP-056902</t>
+  </si>
+  <si>
+    <t>LP-056911</t>
+  </si>
+  <si>
+    <t>LP-056926</t>
+  </si>
+  <si>
+    <t>LP-056943</t>
+  </si>
+  <si>
+    <t>LP-057026</t>
+  </si>
+  <si>
+    <t>LP-057135</t>
+  </si>
+  <si>
+    <t>LP-057151</t>
+  </si>
+  <si>
+    <t>LP-057152</t>
+  </si>
+  <si>
+    <t>LP-057155</t>
+  </si>
+  <si>
+    <t>LP-057170</t>
+  </si>
+  <si>
+    <t>LP-057179</t>
+  </si>
+  <si>
+    <t>LP-057208</t>
+  </si>
+  <si>
+    <t>LP-057211</t>
+  </si>
+  <si>
+    <t>LP-057224</t>
+  </si>
+  <si>
+    <t>LP-057225</t>
+  </si>
+  <si>
+    <t>LP-057256</t>
+  </si>
+  <si>
+    <t>LP-057257</t>
+  </si>
+  <si>
+    <t>LP-057304</t>
+  </si>
+  <si>
+    <t>LP-057307</t>
+  </si>
+  <si>
+    <t>LP-057310</t>
+  </si>
+  <si>
+    <t>LP-057323</t>
+  </si>
+  <si>
+    <t>LP-057380</t>
+  </si>
+  <si>
+    <t>LP-057403</t>
+  </si>
+  <si>
+    <t>LP-057549</t>
+  </si>
+  <si>
+    <t>LP-057706</t>
+  </si>
+  <si>
+    <t>LP-057080</t>
+  </si>
+  <si>
+    <t>LP-057050</t>
+  </si>
+  <si>
+    <t>LP-057048</t>
+  </si>
+  <si>
+    <t>LP-057041</t>
+  </si>
+  <si>
+    <t>LP-057040</t>
+  </si>
+  <si>
+    <t>LP-056900</t>
+  </si>
+  <si>
+    <t>LP-056899</t>
+  </si>
+  <si>
+    <t>LP-056840</t>
+  </si>
+  <si>
+    <t>LP-056839</t>
+  </si>
+  <si>
+    <t>LP-056838</t>
+  </si>
+  <si>
+    <t>LP-056837</t>
+  </si>
+  <si>
+    <t>LP-056717</t>
+  </si>
+  <si>
+    <t>LP-056668</t>
+  </si>
+  <si>
+    <t>LP-056666</t>
+  </si>
+  <si>
+    <t>LP-056623</t>
+  </si>
+  <si>
+    <t>LP-056622</t>
+  </si>
+  <si>
+    <t>LP-056620</t>
+  </si>
+  <si>
+    <t>LP-056538</t>
+  </si>
+  <si>
+    <t>LP-056525</t>
+  </si>
+  <si>
+    <t>LP-056513</t>
+  </si>
+  <si>
+    <t>LP-056512</t>
+  </si>
+  <si>
+    <t>LP-056507</t>
+  </si>
+  <si>
+    <t>LP-056496</t>
+  </si>
+  <si>
+    <t>LP-056412</t>
+  </si>
+  <si>
+    <t>LP-056411</t>
+  </si>
+  <si>
+    <t>LP-056380</t>
+  </si>
+  <si>
+    <t>LP-056118</t>
+  </si>
+  <si>
+    <t>LP-056115</t>
+  </si>
+  <si>
+    <t>LP-056048</t>
+  </si>
+  <si>
+    <t>LP-056047</t>
+  </si>
+  <si>
+    <t>LP-055953</t>
+  </si>
+  <si>
+    <t>LP-055951</t>
+  </si>
+  <si>
+    <t>LP-055945</t>
+  </si>
+  <si>
+    <t>LP-055834</t>
+  </si>
+  <si>
+    <t>LP-055788</t>
+  </si>
+  <si>
+    <t>LP-055764</t>
+  </si>
+  <si>
+    <t>LP-055763</t>
+  </si>
+  <si>
+    <t>LP-055762</t>
+  </si>
+  <si>
+    <t>LP-055681</t>
+  </si>
+  <si>
+    <t>LP-055397</t>
+  </si>
+  <si>
+    <t>LP-055380</t>
+  </si>
+  <si>
+    <t>LP-055356</t>
+  </si>
+  <si>
+    <t>LP-054974</t>
+  </si>
+  <si>
+    <t>LP-054958</t>
+  </si>
+  <si>
+    <t>LP-054602</t>
+  </si>
+  <si>
+    <t>LP-054601</t>
+  </si>
+  <si>
+    <t>LP-054542</t>
+  </si>
+  <si>
+    <t>LP-053607</t>
+  </si>
+  <si>
+    <t>LP-053408</t>
+  </si>
+  <si>
+    <t>LP-053162</t>
+  </si>
+  <si>
+    <t>LP-052987</t>
+  </si>
+  <si>
+    <t>LP-052207</t>
+  </si>
+  <si>
+    <t>LP-051346</t>
+  </si>
+  <si>
+    <t>LP-051343</t>
+  </si>
+  <si>
+    <t>LP-051139</t>
+  </si>
+  <si>
+    <t>LP-050866</t>
+  </si>
+  <si>
+    <t>LP-049367</t>
+  </si>
+  <si>
+    <t>LP-049116</t>
+  </si>
+  <si>
+    <t>LP-045268</t>
+  </si>
+  <si>
+    <t>LP-052737</t>
+  </si>
+  <si>
+    <t>LP-053805</t>
+  </si>
+  <si>
+    <t>LP-053842</t>
+  </si>
+  <si>
+    <t>LP-054501</t>
+  </si>
+  <si>
+    <t>LP-055035</t>
+  </si>
+  <si>
+    <t>LP-055095</t>
+  </si>
+  <si>
+    <t>LP-055146</t>
+  </si>
+  <si>
+    <t>LP-055163</t>
+  </si>
+  <si>
+    <t>LP-055234</t>
+  </si>
+  <si>
+    <t>LP-055507</t>
+  </si>
+  <si>
+    <t>LP-055691</t>
+  </si>
+  <si>
+    <t>LP-055639</t>
+  </si>
+  <si>
+    <t>LP-055732</t>
+  </si>
+  <si>
+    <t>LP-055774</t>
+  </si>
+  <si>
+    <t>LP-055780</t>
+  </si>
+  <si>
+    <t>LP-055802</t>
+  </si>
+  <si>
+    <t>LP-055860</t>
+  </si>
+  <si>
+    <t>LP-055913</t>
+  </si>
+  <si>
+    <t>LP-055934</t>
+  </si>
+  <si>
+    <t>LP-056064</t>
+  </si>
+  <si>
+    <t>LP-056171</t>
+  </si>
+  <si>
+    <t>LP-056172</t>
+  </si>
+  <si>
+    <t>LP-056173</t>
+  </si>
+  <si>
+    <t>LP-056208</t>
+  </si>
+  <si>
+    <t>LP-056270</t>
+  </si>
+  <si>
+    <t>LP-056305</t>
+  </si>
+  <si>
+    <t>LP-056306</t>
+  </si>
+  <si>
+    <t>LP-056429</t>
+  </si>
+  <si>
+    <t>LP-056430</t>
+  </si>
+  <si>
+    <t>LP-056431</t>
+  </si>
+  <si>
+    <t>LP-056600</t>
+  </si>
+  <si>
+    <t>LP-056706</t>
+  </si>
+  <si>
+    <t>LP-056707</t>
+  </si>
+  <si>
+    <t>LP-056833</t>
+  </si>
+  <si>
+    <t>LP-056887</t>
+  </si>
+  <si>
+    <t>LP-056893</t>
+  </si>
+  <si>
+    <t>LP-056918</t>
+  </si>
+  <si>
+    <t>LP-056946</t>
+  </si>
+  <si>
+    <t>LP-057018</t>
+  </si>
+  <si>
+    <t>LP-057034</t>
+  </si>
+  <si>
+    <t>LP-057082</t>
+  </si>
+  <si>
+    <t>LP-057139</t>
+  </si>
+  <si>
+    <t>LP-057158</t>
+  </si>
+  <si>
+    <t>LP-057159</t>
+  </si>
+  <si>
+    <t>LP-057172</t>
+  </si>
+  <si>
+    <t>LP-057173</t>
+  </si>
+  <si>
+    <t>LP-057205</t>
+  </si>
+  <si>
+    <t>LP-057206</t>
+  </si>
+  <si>
+    <t>LP-057227</t>
+  </si>
+  <si>
+    <t>LP-057228</t>
+  </si>
+  <si>
+    <t>LP-057229</t>
+  </si>
+  <si>
+    <t>LP-057230</t>
+  </si>
+  <si>
+    <t>LP-057231</t>
+  </si>
+  <si>
+    <t>LP-057232</t>
+  </si>
+  <si>
+    <t>LP-057253</t>
+  </si>
+  <si>
+    <t>LP-057269</t>
+  </si>
+  <si>
+    <t>LP-057270</t>
+  </si>
+  <si>
+    <t>LP-057315</t>
+  </si>
+  <si>
+    <t>LP-057384</t>
+  </si>
+  <si>
+    <t>LP-057473</t>
+  </si>
+  <si>
+    <t>LP-057486</t>
+  </si>
+  <si>
+    <t>LP-057518</t>
+  </si>
+  <si>
+    <t>LP-057599</t>
+  </si>
+  <si>
+    <t>LP-057602</t>
+  </si>
+  <si>
+    <t>LP-057631</t>
+  </si>
+  <si>
+    <t>LP-057633</t>
+  </si>
+  <si>
+    <t>LP-057654</t>
+  </si>
+  <si>
+    <t>LP-057694</t>
+  </si>
+  <si>
+    <t>LP-057695</t>
+  </si>
+  <si>
+    <t>LP-057696</t>
+  </si>
+  <si>
+    <t>LP-057722</t>
+  </si>
+  <si>
+    <t>LP-057726</t>
+  </si>
+  <si>
+    <t>LP-057727</t>
+  </si>
+  <si>
+    <t>LP-057733</t>
+  </si>
+  <si>
+    <t>LP-057788</t>
+  </si>
+  <si>
+    <t>LP-057789</t>
+  </si>
+  <si>
+    <t>LP-057822</t>
+  </si>
+  <si>
+    <t>LP-050553</t>
+  </si>
+  <si>
+    <t>LP-054012</t>
+  </si>
+  <si>
+    <t>LP-054732</t>
+  </si>
+  <si>
+    <t>LP-056667</t>
+  </si>
+  <si>
+    <t>LP-056516</t>
+  </si>
+  <si>
+    <t>LP-056912</t>
+  </si>
+  <si>
+    <t>LP-056962</t>
+  </si>
+  <si>
+    <t>LP-058191</t>
+  </si>
+  <si>
+    <t>LP-058177</t>
+  </si>
+  <si>
+    <t>LP-058023</t>
+  </si>
+  <si>
+    <t>LP-058022</t>
+  </si>
+  <si>
+    <t>LP-057910</t>
+  </si>
+  <si>
+    <t>LP-057890</t>
+  </si>
+  <si>
+    <t>LP-057878</t>
+  </si>
+  <si>
+    <t>LP-057868</t>
+  </si>
+  <si>
+    <t>LP-057867</t>
+  </si>
+  <si>
+    <t>LP-057861</t>
+  </si>
+  <si>
+    <t>LP-057860</t>
+  </si>
+  <si>
+    <t>LP-057856</t>
+  </si>
+  <si>
+    <t>LP-057849</t>
+  </si>
+  <si>
+    <t>LP-057844</t>
+  </si>
+  <si>
+    <t>LP-057840</t>
+  </si>
+  <si>
+    <t>LP-057838</t>
+  </si>
+  <si>
+    <t>LP-057825</t>
+  </si>
+  <si>
+    <t>LP-057774</t>
+  </si>
+  <si>
+    <t>LP-057728</t>
+  </si>
+  <si>
+    <t>LP-057698</t>
+  </si>
+  <si>
+    <t>LP-057659</t>
+  </si>
+  <si>
+    <t>LP-057658</t>
+  </si>
+  <si>
+    <t>LP-057657</t>
+  </si>
+  <si>
+    <t>LP-057656</t>
+  </si>
+  <si>
+    <t>LP-057655</t>
+  </si>
+  <si>
+    <t>LP-057581</t>
+  </si>
+  <si>
+    <t>LP-057548</t>
+  </si>
+  <si>
+    <t>LP-057387</t>
+  </si>
+  <si>
+    <t>LP-057317</t>
+  </si>
+  <si>
+    <t>LP-057298</t>
+  </si>
+  <si>
+    <t>LP-057297</t>
+  </si>
+  <si>
+    <t>LP-057266</t>
+  </si>
+  <si>
+    <t>LP-057163</t>
+  </si>
+  <si>
+    <t>LP-057113</t>
+  </si>
+  <si>
+    <t>LP-057096</t>
+  </si>
+  <si>
+    <t>LP-057090</t>
+  </si>
+  <si>
+    <t>LP-056934</t>
+  </si>
+  <si>
+    <t>LP-056864</t>
+  </si>
+  <si>
+    <t>LP-056863</t>
+  </si>
+  <si>
+    <t>LP-056725</t>
+  </si>
+  <si>
+    <t>LP-056589</t>
+  </si>
+  <si>
+    <t>LP-056337</t>
+  </si>
+  <si>
+    <t>LP-056181</t>
+  </si>
+  <si>
+    <t>LP-056174</t>
+  </si>
+  <si>
+    <t>LP-056016</t>
+  </si>
+  <si>
+    <t>LP-055572</t>
+  </si>
+  <si>
+    <t>LP-055526</t>
+  </si>
+  <si>
+    <t>LP-055450</t>
+  </si>
+  <si>
+    <t>LP-055217</t>
+  </si>
+  <si>
+    <t>LP-058258</t>
+  </si>
+  <si>
+    <t>LP-057925</t>
+  </si>
+  <si>
+    <t>LP-057739</t>
+  </si>
+  <si>
+    <t>LP-057681</t>
+  </si>
+  <si>
+    <t>LP-057680</t>
+  </si>
+  <si>
+    <t>LP-057606</t>
+  </si>
+  <si>
+    <t>LP-057605</t>
+  </si>
+  <si>
+    <t>LP-057597</t>
+  </si>
+  <si>
+    <t>LP-057580</t>
+  </si>
+  <si>
+    <t>LP-057579</t>
+  </si>
+  <si>
+    <t>LP-057472</t>
+  </si>
+  <si>
+    <t>LP-057455</t>
+  </si>
+  <si>
+    <t>LP-057442</t>
+  </si>
+  <si>
+    <t>LP-057443</t>
+  </si>
+  <si>
+    <t>LP-057441</t>
+  </si>
+  <si>
+    <t>LP-057432</t>
+  </si>
+  <si>
+    <t>LP-057400</t>
+  </si>
+  <si>
+    <t>LP-057295</t>
+  </si>
+  <si>
+    <t>LP-057212</t>
+  </si>
+  <si>
+    <t>LP-057210</t>
+  </si>
+  <si>
+    <t>LP-057185</t>
+  </si>
+  <si>
+    <t>LP-057183</t>
+  </si>
+  <si>
+    <t>LP-057182</t>
+  </si>
+  <si>
+    <t>LP-057181</t>
+  </si>
+  <si>
+    <t>LP-057153</t>
+  </si>
+  <si>
+    <t>LP-057138</t>
+  </si>
+  <si>
+    <t>LP-057131</t>
+  </si>
+  <si>
+    <t>LP-057123</t>
+  </si>
+  <si>
+    <t>LP-057118</t>
+  </si>
+  <si>
+    <t>LP-057097</t>
+  </si>
+  <si>
+    <t>LP-057081</t>
+  </si>
+  <si>
+    <t>LP-057063</t>
+  </si>
+  <si>
+    <t>LP-056931</t>
+  </si>
+  <si>
+    <t>LP-056928</t>
+  </si>
+  <si>
+    <t>LP-056923</t>
+  </si>
+  <si>
+    <t>LP-056916</t>
+  </si>
+  <si>
+    <t>LP-056915</t>
+  </si>
+  <si>
+    <t>LP-056913</t>
+  </si>
+  <si>
+    <t>LP-056906</t>
+  </si>
+  <si>
+    <t>LP-056764</t>
+  </si>
+  <si>
+    <t>LP-056573</t>
+  </si>
+  <si>
+    <t>LP-056460</t>
+  </si>
+  <si>
+    <t>LP-056427</t>
+  </si>
+  <si>
+    <t>LP-056426</t>
+  </si>
+  <si>
+    <t>LP-056343</t>
+  </si>
+  <si>
+    <t>LP-056336</t>
+  </si>
+  <si>
+    <t>LP-056345</t>
+  </si>
+  <si>
+    <t>LP-056341</t>
+  </si>
+  <si>
+    <t>LP-056344</t>
+  </si>
+  <si>
+    <t>LP-056254</t>
+  </si>
+  <si>
+    <t>LP-056252</t>
+  </si>
+  <si>
+    <t>LP-056156</t>
+  </si>
+  <si>
+    <t>LP-056155</t>
+  </si>
+  <si>
+    <t>LP-056111</t>
+  </si>
+  <si>
+    <t>LP-056100</t>
+  </si>
+  <si>
+    <t>LP-055928</t>
+  </si>
+  <si>
+    <t>LP-055637</t>
+  </si>
+  <si>
+    <t>LP-055614</t>
+  </si>
+  <si>
+    <t>LP-054470</t>
+  </si>
+  <si>
+    <t>LP-054070</t>
+  </si>
+  <si>
+    <t>LP-051534</t>
+  </si>
+  <si>
+    <t>LP-054814</t>
+  </si>
+  <si>
+    <t>LP-053046</t>
+  </si>
+  <si>
+    <t>LP-054923</t>
+  </si>
+  <si>
+    <t>LP-054924</t>
+  </si>
+  <si>
+    <t>LP-056481</t>
+  </si>
+  <si>
+    <t>LP-056049</t>
+  </si>
+  <si>
+    <t>LP-054916</t>
+  </si>
+  <si>
+    <t>LP-056093</t>
+  </si>
+  <si>
+    <t>LP-046952</t>
+  </si>
+  <si>
+    <t>LP-056276</t>
+  </si>
+  <si>
+    <t>LP-052184</t>
+  </si>
+  <si>
+    <t>LP-051632</t>
+  </si>
+  <si>
+    <t>LP-055786</t>
+  </si>
+  <si>
+    <t>LP-049613</t>
+  </si>
+  <si>
+    <t>LP-056606</t>
+  </si>
+  <si>
+    <t>LP-056773</t>
+  </si>
+  <si>
+    <t>LP-049055</t>
+  </si>
+  <si>
+    <t>LP-050270</t>
+  </si>
+  <si>
+    <t>LP-057039</t>
+  </si>
+  <si>
+    <t>LP-056492</t>
+  </si>
+  <si>
+    <t>LP-056491</t>
+  </si>
+  <si>
+    <t>LP-056530</t>
+  </si>
+  <si>
+    <t>LP-056480</t>
+  </si>
+  <si>
+    <t>LP-057008</t>
+  </si>
+  <si>
+    <t>LP-056996</t>
+  </si>
+  <si>
+    <t>LP-056932</t>
+  </si>
+  <si>
+    <t>LP-055245</t>
+  </si>
+  <si>
+    <t>LP-053078</t>
+  </si>
+  <si>
+    <t>LP-056604</t>
+  </si>
+  <si>
+    <t>LP-051398</t>
+  </si>
+  <si>
+    <t>LP-057300</t>
+  </si>
+  <si>
+    <t>LP-054355</t>
+  </si>
+  <si>
+    <t>LP-055324</t>
+  </si>
+  <si>
+    <t>LP-053048</t>
+  </si>
+  <si>
+    <t>LP-057301</t>
+  </si>
+  <si>
+    <t>LP-057077</t>
+  </si>
+  <si>
+    <t>LP-057572</t>
+  </si>
+  <si>
+    <t>LP-058183</t>
+  </si>
+  <si>
+    <t>LP-058184</t>
+  </si>
+  <si>
+    <t>LP-057136</t>
+  </si>
+  <si>
+    <t>LP-055616</t>
+  </si>
+  <si>
+    <t>LP-056929</t>
+  </si>
+  <si>
+    <t>LP-056261</t>
+  </si>
+  <si>
+    <t>LP-055964</t>
+  </si>
+  <si>
+    <t>LP-056921</t>
+  </si>
+  <si>
+    <t>LP-057693</t>
+  </si>
+  <si>
+    <t>LP-057260</t>
+  </si>
+  <si>
+    <t>LP-057035</t>
+  </si>
+  <si>
+    <t>LP-058330</t>
+  </si>
+  <si>
+    <t>LP-058093</t>
+  </si>
+  <si>
+    <t>LP-057480</t>
+  </si>
+  <si>
+    <t>LP-057445</t>
+  </si>
+  <si>
+    <t>LP-058181</t>
+  </si>
+  <si>
+    <t>LP-058092</t>
+  </si>
+  <si>
+    <t>LP-057866</t>
+  </si>
+  <si>
+    <t>LP-057978</t>
+  </si>
+  <si>
+    <t>LP-058172</t>
+  </si>
+  <si>
+    <t>LP-057088</t>
+  </si>
+  <si>
+    <t>LP-057079</t>
+  </si>
+  <si>
+    <t>LP-058185</t>
+  </si>
+  <si>
+    <t>LP-057386</t>
+  </si>
+  <si>
+    <t>LP-057184</t>
+  </si>
+  <si>
+    <t>LP-056956</t>
+  </si>
+  <si>
+    <t>LP-057529</t>
+  </si>
+  <si>
+    <t>LP-057291</t>
+  </si>
+  <si>
+    <t>LP-057697</t>
+  </si>
+  <si>
+    <t>LP-057769</t>
+  </si>
+  <si>
+    <t>LP-057106</t>
+  </si>
+  <si>
+    <t>LP-057107</t>
+  </si>
+  <si>
+    <t>LP-057595</t>
+  </si>
+  <si>
+    <t>LP-057289</t>
+  </si>
+  <si>
+    <t>LP-057882</t>
+  </si>
+  <si>
+    <t>LP-057850</t>
+  </si>
+  <si>
+    <t>LP-058178</t>
+  </si>
+  <si>
+    <t>LP-057381</t>
+  </si>
+  <si>
+    <t>LP-056731</t>
+  </si>
+  <si>
+    <t>LP-057592</t>
+  </si>
+  <si>
+    <t>LP-056777</t>
+  </si>
+  <si>
+    <t>LP-043234</t>
+  </si>
+  <si>
+    <t>LP-055118</t>
+  </si>
+  <si>
+    <t>LP-058190</t>
+  </si>
+  <si>
+    <t>LP-057306</t>
+  </si>
+  <si>
+    <t>LP-057907</t>
+  </si>
+  <si>
+    <t>LP-056391</t>
+  </si>
+  <si>
+    <t>LP-053103</t>
+  </si>
+  <si>
+    <t>LP-054538</t>
+  </si>
+  <si>
+    <t>LP-056845</t>
+  </si>
+  <si>
+    <t>LP-051365</t>
+  </si>
+  <si>
+    <t>LP-056117</t>
+  </si>
+  <si>
+    <t>LP-051399</t>
+  </si>
+  <si>
+    <t>LP-055504</t>
+  </si>
+  <si>
+    <t>LP-057557</t>
+  </si>
+  <si>
+    <t>LP-057373</t>
+  </si>
+  <si>
+    <t>LP-052979</t>
+  </si>
+  <si>
+    <t>LP-056323</t>
+  </si>
+  <si>
+    <t>LP-056262</t>
+  </si>
+  <si>
+    <t>LP-057764</t>
+  </si>
+  <si>
+    <t>LP-057043</t>
+  </si>
+  <si>
+    <t>LP-057763</t>
+  </si>
+  <si>
+    <t>LP-056522</t>
+  </si>
+  <si>
+    <t>LP-055819</t>
+  </si>
+  <si>
+    <t>LP-051692</t>
+  </si>
+  <si>
+    <t>LP-055170</t>
+  </si>
+  <si>
+    <t>LP-055661</t>
+  </si>
+  <si>
+    <t>LP-051148</t>
+  </si>
+  <si>
+    <t>LP-053036</t>
+  </si>
+  <si>
+    <t>LP-052913</t>
+  </si>
+  <si>
+    <t>LP-056770</t>
+  </si>
+  <si>
+    <t>LP-055667</t>
+  </si>
+  <si>
+    <t>LP-056608</t>
+  </si>
+  <si>
+    <t>LP-056831</t>
+  </si>
+  <si>
+    <t>LP-054822</t>
+  </si>
+  <si>
+    <t>LP-056511</t>
+  </si>
+  <si>
+    <t>LP-052768</t>
+  </si>
+  <si>
+    <t>LP-055201</t>
+  </si>
+  <si>
+    <t>LP-057371</t>
+  </si>
+  <si>
+    <t>LP-057537</t>
+  </si>
+  <si>
+    <t>LP-057372</t>
+  </si>
+  <si>
+    <t>LP-053935</t>
+  </si>
+  <si>
+    <t>LP-053402</t>
+  </si>
+  <si>
+    <t>LP-054831</t>
+  </si>
+  <si>
+    <t>LP-056836</t>
+  </si>
+  <si>
+    <t>LP-057949</t>
+  </si>
+  <si>
+    <t>LP-056397</t>
+  </si>
+  <si>
+    <t>LP-057340</t>
+  </si>
+  <si>
+    <t>LP-057937</t>
+  </si>
+  <si>
+    <t>LP-057936</t>
+  </si>
+  <si>
+    <t>LP-053608</t>
+  </si>
+  <si>
+    <t>LP-054579</t>
+  </si>
+  <si>
+    <t>LP-051145</t>
+  </si>
+  <si>
+    <t>LP-056328</t>
+  </si>
+  <si>
+    <t>LP-055674</t>
+  </si>
+  <si>
+    <t>LP-048756</t>
+  </si>
+  <si>
+    <t>LP-055177</t>
+  </si>
+  <si>
+    <t>LP-055737</t>
+  </si>
+  <si>
+    <t>LP-052950</t>
+  </si>
+  <si>
+    <t>LP-057541</t>
+  </si>
+  <si>
+    <t>LP-058186</t>
+  </si>
+  <si>
+    <t>LP-055176</t>
+  </si>
+  <si>
+    <t>LP-057218</t>
+  </si>
+  <si>
+    <t>LP-054926</t>
+  </si>
+  <si>
+    <t>LP-057701</t>
+  </si>
+  <si>
+    <t>LP-056452</t>
+  </si>
+  <si>
+    <t>LP-056321</t>
+  </si>
+  <si>
+    <t>LP-056960</t>
+  </si>
+  <si>
+    <t>LP-055342</t>
+  </si>
+  <si>
+    <t>LP-057214</t>
+  </si>
+  <si>
+    <t>LP-056399</t>
+  </si>
+  <si>
+    <t>LP-057125</t>
+  </si>
+  <si>
+    <t>LP-056578</t>
+  </si>
+  <si>
+    <t>LP-056719</t>
+  </si>
+  <si>
+    <t>LP-057760</t>
+  </si>
+  <si>
+    <t>LP-057545</t>
+  </si>
+  <si>
+    <t>LP-057624</t>
+  </si>
+  <si>
+    <t>LP-057622</t>
+  </si>
+  <si>
+    <t>LP-057623</t>
+  </si>
+  <si>
+    <t>LP-050411</t>
+  </si>
+  <si>
+    <t>LP-053934</t>
+  </si>
+  <si>
+    <t>LP-054611</t>
+  </si>
+  <si>
+    <t>LP-057166</t>
+  </si>
+  <si>
+    <t>LP-055182</t>
+  </si>
+  <si>
+    <t>LP-056537</t>
+  </si>
+  <si>
+    <t>LP-057374</t>
+  </si>
+  <si>
+    <t>LP-057449</t>
+  </si>
+  <si>
+    <t>LP-057539</t>
+  </si>
+  <si>
+    <t>LP-056881</t>
+  </si>
+  <si>
+    <t>LP-057337</t>
+  </si>
+  <si>
+    <t>LP-056607</t>
+  </si>
+  <si>
+    <t>LP-055337</t>
+  </si>
+  <si>
+    <t>LP-055325</t>
+  </si>
+  <si>
+    <t>LP-056526</t>
+  </si>
+  <si>
+    <t>LP-057339</t>
+  </si>
+  <si>
+    <t>LP-056224</t>
+  </si>
+  <si>
+    <t>LP-051055</t>
+  </si>
+  <si>
+    <t>LP-055698</t>
+  </si>
+  <si>
+    <t>LP-056008</t>
+  </si>
+  <si>
+    <t>LP-051050</t>
+  </si>
+  <si>
+    <t>LP-055364</t>
+  </si>
+  <si>
+    <t>LP-055074</t>
+  </si>
+  <si>
+    <t>LP-056841</t>
+  </si>
+  <si>
+    <t>LP-057341</t>
   </si>
 </sst>
 </file>
@@ -4457,7 +6125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1376"/>
+  <dimension ref="A1:B1944"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -11347,6 +13015,2846 @@
         <v>1364</v>
       </c>
     </row>
+    <row r="1377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1377" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1378" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1379" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1380" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1381" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1382" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1383" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1384" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1385" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1386" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1387" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1388" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1389" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1390" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1391" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1392" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1393" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1394" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1395" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1396" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1397" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1398" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1399" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1400" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1401" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1402" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1403" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1404" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1405" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1406" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1407" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1408" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1409" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1410" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1411" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1412" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1413" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1414" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1415" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1416" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1417" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1418" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1419" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1420" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1421" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1422" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1423" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1424" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1425" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1426" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1427" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1428" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1429" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1430" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1431" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1432" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1433" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1434" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1435" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1436" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1437" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1438" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1439" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1440" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1441" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1442" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1443" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1444" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1445" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1446" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1447" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1448" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1449" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1450" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1451" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1452" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1453" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1454" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1455" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1456" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1457" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1458" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1459" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1460" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1461" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1462" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1463" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1464" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1465" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1466" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1467" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1468" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1469" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1470" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1471" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1472" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1473" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1474" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1475" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1476" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1477" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1478" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1479" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1480" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1481" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1482" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1483" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1484" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1485" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1486" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1487" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1488" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1489" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1490" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1491" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1492" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1493" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1494" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1495" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1496" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1497" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1498" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1499" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1500" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1501" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1502" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1503" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1504" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1505" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1506" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1507" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1508" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1509" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1510" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1511" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1512" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1513" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1514" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1515" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1516" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1517" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1518" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1519" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1520" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1521" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1522" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1523" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1524" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1525" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1526" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1527" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1528" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1529" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1530" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1531" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1532" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1533" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1534" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1535" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1536" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1537" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1538" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1539" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1540" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1541" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1542" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1543" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1544" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1545" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1546" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1547" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1548" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1549" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1550" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1551" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1552" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1553" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1554" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1555" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1556" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1557" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1558" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1559" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1560" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1561" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1562" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1563" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1564" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1565" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1566" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1567" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1568" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1569" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1570" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1571" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1572" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1573" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1574" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1575" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1576" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1577" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1578" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1579" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1580" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1581" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1582" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1583" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1584" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1585" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1586" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1587" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1588" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1589" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1590" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1591" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1592" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1593" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1594" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1595" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1596" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1597" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1598" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1599" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1600" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1601" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1602" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1603" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1604" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1605" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1606" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1607" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1608" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1609" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1610" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1611" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1612" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1613" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1614" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1615" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1616" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1617" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1618" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1619" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1620" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1621" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1622" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1623" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1624" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1625" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1626" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1627" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1628" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1629" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1630" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1631" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1632" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1633" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1634" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1635" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1636" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1637" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1638" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1639" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1640" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1641" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1642" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1643" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1644" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1645" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1646" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1647" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1648" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1649" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1650" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1651" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1652" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1653" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1654" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1655" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1656" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1657" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1658" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1659" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1660" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1661" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1662" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1663" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1664" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1665" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1666" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1667" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1668" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1669" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1670" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1671" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1672" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1673" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1674" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1675" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1676" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1677" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1678" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1679" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1680" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1681" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1682" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1683" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1684" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1685" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1686" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1687" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1688" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1689" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1690" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1691" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1692" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1693" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1694" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1695" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1696" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1697" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1698" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1699" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1700" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1701" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1702" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1703" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1704" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1705" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1706" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1707" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1708" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1709" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1710" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1711" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1712" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1713" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1714" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1715" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1716" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1717" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1718" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1719" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1720" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1721" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1722" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1723" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1724" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1725" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1726" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1727" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1728" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1729" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1730" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1731" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1732" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1733" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1734" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1735" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1736" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1737" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1738" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1739" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1740" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1741" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1742" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1743" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1744" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1745" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1746" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1747" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1748" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1749" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1750" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1751" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1752" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1753" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1754" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1755" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1756" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1757" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1758" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1759" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1760" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1761" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1762" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1763" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1764" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1765" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1766" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1767" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1768" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1769" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1770" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1771" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1772" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1773" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1774" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1775" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1776" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1777" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1778" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1779" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1780" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1781" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1782" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1783" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1784" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1785" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1786" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1787" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1788" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1789" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1790" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1791" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1792" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1793" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1794" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1795" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1796" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1797" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1798" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1799" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1800" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1801" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1802" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1803" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1804" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1805" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1806" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1807" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1808" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1809" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1810" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1811" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1812" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1813" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1814" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1815" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1816" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1817" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1818" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1819" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1820" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1821" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1822" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1823" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1824" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1825" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1826" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1827" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1828" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1829" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1830" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1831" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1832" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1833" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1834" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1835" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1836" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1837" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1838" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1839" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1840" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1841" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1842" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1843" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1844" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1845" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1846" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1847" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1848" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1849" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1850" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1851" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1852" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1853" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1854" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1855" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1856" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1857" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1858" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1859" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1860" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1861" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1862" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1863" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1864" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1865" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1866" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1867" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1868" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1869" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1870" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1871" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1872" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1873" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1874" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1875" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1876" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1877" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1878" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1879" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1880" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1881" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1882" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1883" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1884" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1885" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1886" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1887" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1888" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1889" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1890" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1891" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1892" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1893" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1894" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1895" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1896" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1897" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1898" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1899" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1900" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1901" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1902" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1903" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1904" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1905" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1906" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1907" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1908" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1909" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1910" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1911" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1912" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1913" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1914" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1915" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1916" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1917" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1918" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1919" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1920" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1921" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1922" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1923" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1924" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1925" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1926" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1927" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1928" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1929" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1930" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1931" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1932" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1933" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1934" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1935" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1936" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1937" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1938" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1939" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1940" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1941" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1942" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1943" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1944" t="s">
+        <v>1920</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/99 - Excels/Open-LPs.xlsx
+++ b/99 - Excels/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8870A0AA-4BA2-4013-BA91-D1919544DEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57D7E0B-5F0F-463C-A937-F44D18EA2231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="1921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="2031">
   <si>
     <t>LP</t>
   </si>
@@ -5786,6 +5786,336 @@
   </si>
   <si>
     <t>LP-057341</t>
+  </si>
+  <si>
+    <t>LP-045438</t>
+  </si>
+  <si>
+    <t>LP-045668</t>
+  </si>
+  <si>
+    <t>LP-045931</t>
+  </si>
+  <si>
+    <t>LP-051052</t>
+  </si>
+  <si>
+    <t>LP-052741</t>
+  </si>
+  <si>
+    <t>LP-055210</t>
+  </si>
+  <si>
+    <t>LP-055787</t>
+  </si>
+  <si>
+    <t>LP-055791</t>
+  </si>
+  <si>
+    <t>LP-055898</t>
+  </si>
+  <si>
+    <t>LP-056004</t>
+  </si>
+  <si>
+    <t>LP-056071</t>
+  </si>
+  <si>
+    <t>LP-056255</t>
+  </si>
+  <si>
+    <t>LP-056580</t>
+  </si>
+  <si>
+    <t>LP-056612</t>
+  </si>
+  <si>
+    <t>LP-056613</t>
+  </si>
+  <si>
+    <t>LP-056796</t>
+  </si>
+  <si>
+    <t>LP-056802</t>
+  </si>
+  <si>
+    <t>LP-056879</t>
+  </si>
+  <si>
+    <t>LP-056914</t>
+  </si>
+  <si>
+    <t>LP-056927</t>
+  </si>
+  <si>
+    <t>LP-056939</t>
+  </si>
+  <si>
+    <t>LP-056955</t>
+  </si>
+  <si>
+    <t>LP-057084</t>
+  </si>
+  <si>
+    <t>LP-057086</t>
+  </si>
+  <si>
+    <t>LP-057104</t>
+  </si>
+  <si>
+    <t>LP-057105</t>
+  </si>
+  <si>
+    <t>LP-057119</t>
+  </si>
+  <si>
+    <t>LP-057175</t>
+  </si>
+  <si>
+    <t>LP-057258</t>
+  </si>
+  <si>
+    <t>LP-057276</t>
+  </si>
+  <si>
+    <t>LP-057364</t>
+  </si>
+  <si>
+    <t>LP-057438</t>
+  </si>
+  <si>
+    <t>LP-057453</t>
+  </si>
+  <si>
+    <t>LP-057454</t>
+  </si>
+  <si>
+    <t>LP-057556</t>
+  </si>
+  <si>
+    <t>LP-057665</t>
+  </si>
+  <si>
+    <t>LP-057724</t>
+  </si>
+  <si>
+    <t>LP-057809</t>
+  </si>
+  <si>
+    <t>LP-057839</t>
+  </si>
+  <si>
+    <t>LP-057919</t>
+  </si>
+  <si>
+    <t>LP-058088</t>
+  </si>
+  <si>
+    <t>LP-058121</t>
+  </si>
+  <si>
+    <t>LP-058163</t>
+  </si>
+  <si>
+    <t>LP-058278</t>
+  </si>
+  <si>
+    <t>LP-058366</t>
+  </si>
+  <si>
+    <t>LP-058368</t>
+  </si>
+  <si>
+    <t>LP-058473</t>
+  </si>
+  <si>
+    <t>LP-044722</t>
+  </si>
+  <si>
+    <t>LP-047645</t>
+  </si>
+  <si>
+    <t>LP-049330</t>
+  </si>
+  <si>
+    <t>LP-050124</t>
+  </si>
+  <si>
+    <t>LP-051721</t>
+  </si>
+  <si>
+    <t>LP-052910</t>
+  </si>
+  <si>
+    <t>LP-052989</t>
+  </si>
+  <si>
+    <t>LP-053261</t>
+  </si>
+  <si>
+    <t>LP-053306</t>
+  </si>
+  <si>
+    <t>LP-055343</t>
+  </si>
+  <si>
+    <t>LP-055346</t>
+  </si>
+  <si>
+    <t>LP-055496</t>
+  </si>
+  <si>
+    <t>LP-055675</t>
+  </si>
+  <si>
+    <t>LP-055736</t>
+  </si>
+  <si>
+    <t>LP-055745</t>
+  </si>
+  <si>
+    <t>LP-055760</t>
+  </si>
+  <si>
+    <t>LP-055765</t>
+  </si>
+  <si>
+    <t>LP-055793</t>
+  </si>
+  <si>
+    <t>LP-056089</t>
+  </si>
+  <si>
+    <t>LP-056223</t>
+  </si>
+  <si>
+    <t>LP-056263</t>
+  </si>
+  <si>
+    <t>LP-056324</t>
+  </si>
+  <si>
+    <t>LP-056377</t>
+  </si>
+  <si>
+    <t>LP-056384</t>
+  </si>
+  <si>
+    <t>LP-056398</t>
+  </si>
+  <si>
+    <t>LP-056454</t>
+  </si>
+  <si>
+    <t>LP-056486</t>
+  </si>
+  <si>
+    <t>LP-056520</t>
+  </si>
+  <si>
+    <t>LP-056521</t>
+  </si>
+  <si>
+    <t>LP-056536</t>
+  </si>
+  <si>
+    <t>LP-056579</t>
+  </si>
+  <si>
+    <t>LP-056901</t>
+  </si>
+  <si>
+    <t>LP-056975</t>
+  </si>
+  <si>
+    <t>LP-056987</t>
+  </si>
+  <si>
+    <t>LP-057002</t>
+  </si>
+  <si>
+    <t>LP-057093</t>
+  </si>
+  <si>
+    <t>LP-057117</t>
+  </si>
+  <si>
+    <t>LP-057338</t>
+  </si>
+  <si>
+    <t>LP-057378</t>
+  </si>
+  <si>
+    <t>LP-057422</t>
+  </si>
+  <si>
+    <t>LP-057538</t>
+  </si>
+  <si>
+    <t>LP-057686</t>
+  </si>
+  <si>
+    <t>LP-057699</t>
+  </si>
+  <si>
+    <t>LP-057700</t>
+  </si>
+  <si>
+    <t>LP-057729</t>
+  </si>
+  <si>
+    <t>LP-057730</t>
+  </si>
+  <si>
+    <t>LP-057757</t>
+  </si>
+  <si>
+    <t>LP-057762</t>
+  </si>
+  <si>
+    <t>LP-057827</t>
+  </si>
+  <si>
+    <t>LP-057875</t>
+  </si>
+  <si>
+    <t>LP-057876</t>
+  </si>
+  <si>
+    <t>LP-057894</t>
+  </si>
+  <si>
+    <t>LP-057964</t>
+  </si>
+  <si>
+    <t>LP-057982</t>
+  </si>
+  <si>
+    <t>LP-057983</t>
+  </si>
+  <si>
+    <t>LP-057984</t>
+  </si>
+  <si>
+    <t>LP-057986</t>
+  </si>
+  <si>
+    <t>LP-057993</t>
+  </si>
+  <si>
+    <t>LP-058232</t>
+  </si>
+  <si>
+    <t>LP-058233</t>
+  </si>
+  <si>
+    <t>LP-058236</t>
+  </si>
+  <si>
+    <t>LP-058238</t>
+  </si>
+  <si>
+    <t>LP-058244</t>
   </si>
 </sst>
 </file>
@@ -6125,7 +6455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1944"/>
+  <dimension ref="A1:B2056"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -15855,6 +16185,566 @@
         <v>1920</v>
       </c>
     </row>
+    <row r="1945" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1945" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1946" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1947" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1948" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1949" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1950" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1951" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1952" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1953" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1954" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1955" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1956" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1957" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1958" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1959" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1960" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1961" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1962" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1963" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1964" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1965" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1966" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1967" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1968" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1969" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1970" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1971" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1972" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1973" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1974" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1975" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1976" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1977" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1978" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1979" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1980" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1981" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1982" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1983" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1984" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1985" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1986" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1987" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1988" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1989" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1990" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1991" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1992" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1993" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1994" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1995" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1996" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1997" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1998" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1999" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2000" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2001" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2002" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2003" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2004" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2005" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2006" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2007" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2008" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2009" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2010" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2011" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2012" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2013" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2014" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2015" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2016" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2017" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2018" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2019" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2020" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2021" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2022" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2023" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2024" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2025" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2026" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2027" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2028" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2029" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2030" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2031" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2032" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2033" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2034" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2035" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2036" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2037" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2038" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2039" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2040" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2041" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2042" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2043" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2044" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2045" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2046" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2047" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2048" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2049" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2050" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2051" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2052" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2053" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2054" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2055" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2056" t="s">
+        <v>2030</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
